--- a/Catalogo JLB.xlsx
+++ b/Catalogo JLB.xlsx
@@ -1,19 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Familia Acosta Alcai\Documents\JLB-Web\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AE284B-F25C-4684-B813-438A630ACDDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="7630" yWindow="1320" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$G$733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$G$733</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3973" uniqueCount="1833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4062" uniqueCount="1856">
   <si>
     <t>ID</t>
   </si>
@@ -5512,51 +5522,136 @@
   </si>
   <si>
     <t>KIT DE FUERZA MOTOR E-7</t>
+  </si>
+  <si>
+    <t>K3480</t>
+  </si>
+  <si>
+    <t>AUXILIARY DRIVE GEAR KIT</t>
+  </si>
+  <si>
+    <t>JUEGO SINCRONIZADOR</t>
+  </si>
+  <si>
+    <t>A7254</t>
+  </si>
+  <si>
+    <t>HIGH PERFORMANCE MAINDRIVE GEAR</t>
+  </si>
+  <si>
+    <t>EMBRAGUE</t>
+  </si>
+  <si>
+    <t>GEAR</t>
+  </si>
+  <si>
+    <t>COJINETE</t>
+  </si>
+  <si>
+    <t>EJE PRINCIPAL</t>
+  </si>
+  <si>
+    <t>S3108</t>
+  </si>
+  <si>
+    <t>ENGRANAJE</t>
+  </si>
+  <si>
+    <t>SINCRONIZADOR</t>
+  </si>
+  <si>
+    <t>A7331</t>
+  </si>
+  <si>
+    <t>BUJE</t>
+  </si>
+  <si>
+    <t>RESORTE</t>
+  </si>
+  <si>
+    <t>575KB3303</t>
+  </si>
+  <si>
+    <t>RODAMIENTO AUXILIAR</t>
+  </si>
+  <si>
+    <t>RESORTE SINCRONIZADOR</t>
+  </si>
+  <si>
+    <t>PIÑON DE SOBRE MARCHA</t>
+  </si>
+  <si>
+    <t>PIÑON REDUCTOR</t>
+  </si>
+  <si>
+    <t>PIÑON EJE PRINCIPAL</t>
+  </si>
+  <si>
+    <t>ESPACIDOR EJE AUXILIAR</t>
+  </si>
+  <si>
+    <t>EMBRAGUE SINCRONIZADOR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm-yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm\-yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -5565,7 +5660,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -5581,7 +5676,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -5595,68 +5696,58 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -5846,26 +5937,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G759"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.63"/>
-    <col customWidth="1" min="2" max="2" width="15.5"/>
-    <col customWidth="1" min="3" max="3" width="16.0"/>
-    <col customWidth="1" min="4" max="4" width="57.88"/>
-    <col customWidth="1" min="5" max="5" width="24.13"/>
-    <col customWidth="1" min="6" max="6" width="10.5"/>
-    <col customWidth="1" min="7" max="7" width="50.5"/>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="57.90625" customWidth="1"/>
+    <col min="5" max="5" width="24.08984375" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" customWidth="1"/>
+    <col min="7" max="7" width="50.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5888,7 +5982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
@@ -5908,7 +6002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
@@ -5928,9 +6022,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="7">
-        <v>803725.0</v>
+        <v>803725</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>15</v>
@@ -5948,7 +6042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="7" t="s">
         <v>18</v>
       </c>
@@ -5968,9 +6062,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="7">
-        <v>804256.0</v>
+        <v>804256</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>21</v>
@@ -5988,12 +6082,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="7">
-        <v>804257.0</v>
+        <v>804257</v>
       </c>
       <c r="C7" s="7">
-        <v>2.2662259E7</v>
+        <v>22662259</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>23</v>
@@ -6002,15 +6096,15 @@
         <v>17</v>
       </c>
       <c r="F7" s="7">
-        <v>2.2662259E7</v>
+        <v>22662259</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="7">
-        <v>804300.0</v>
+        <v>804300</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>24</v>
@@ -6028,7 +6122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="7" t="s">
         <v>25</v>
       </c>
@@ -6048,9 +6142,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="7">
-        <v>804298.0</v>
+        <v>804298</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>28</v>
@@ -6068,7 +6162,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="7" t="s">
         <v>30</v>
       </c>
@@ -6088,7 +6182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="7" t="s">
         <v>34</v>
       </c>
@@ -6108,7 +6202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="7" t="s">
         <v>37</v>
       </c>
@@ -6128,12 +6222,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="7">
-        <v>805050.0</v>
+        <v>805050</v>
       </c>
       <c r="C14" s="7">
-        <v>2.0747511E7</v>
+        <v>20747511</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>40</v>
@@ -6142,13 +6236,13 @@
         <v>33</v>
       </c>
       <c r="F14" s="7">
-        <v>2.0747511E7</v>
+        <v>20747511</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="7" t="s">
         <v>41</v>
       </c>
@@ -6168,7 +6262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="7" t="s">
         <v>44</v>
       </c>
@@ -6188,7 +6282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="7" t="s">
         <v>47</v>
       </c>
@@ -6208,12 +6302,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="7">
-        <v>801124.0</v>
+        <v>801124</v>
       </c>
       <c r="C18" s="7">
-        <v>8.5111558E7</v>
+        <v>85111558</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>50</v>
@@ -6222,13 +6316,13 @@
         <v>33</v>
       </c>
       <c r="F18" s="7">
-        <v>8.5111558E7</v>
+        <v>85111558</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="7" t="s">
         <v>51</v>
       </c>
@@ -6248,7 +6342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="7" t="s">
         <v>54</v>
       </c>
@@ -6268,7 +6362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="7" t="s">
         <v>57</v>
       </c>
@@ -6288,7 +6382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="7" t="s">
         <v>60</v>
       </c>
@@ -6308,7 +6402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="7" t="s">
         <v>62</v>
       </c>
@@ -6328,9 +6422,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B24" s="7">
-        <v>803925.0</v>
+        <v>803925</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>65</v>
@@ -6348,9 +6442,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B25" s="7">
-        <v>803926.0</v>
+        <v>803926</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>68</v>
@@ -6368,7 +6462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B26" s="7" t="s">
         <v>70</v>
       </c>
@@ -6388,9 +6482,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B27" s="7">
-        <v>806726.0</v>
+        <v>806726</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>72</v>
@@ -6408,7 +6502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B28" s="7" t="s">
         <v>75</v>
       </c>
@@ -6428,7 +6522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B29" s="7" t="s">
         <v>78</v>
       </c>
@@ -6448,7 +6542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B30" s="7" t="s">
         <v>81</v>
       </c>
@@ -6468,12 +6562,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B31" s="7" t="s">
         <v>84</v>
       </c>
       <c r="C31" s="7">
-        <v>8.5124623E7</v>
+        <v>85124623</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>85</v>
@@ -6482,13 +6576,13 @@
         <v>33</v>
       </c>
       <c r="F31" s="7">
-        <v>8.5124623E7</v>
+        <v>85124623</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B32" s="7" t="s">
         <v>86</v>
       </c>
@@ -6508,7 +6602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B33" s="7" t="s">
         <v>89</v>
       </c>
@@ -6528,7 +6622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B34" s="7" t="s">
         <v>92</v>
       </c>
@@ -6548,7 +6642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B35" s="7" t="s">
         <v>95</v>
       </c>
@@ -6568,7 +6662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B36" s="7" t="s">
         <v>97</v>
       </c>
@@ -6588,7 +6682,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B37" s="7" t="s">
         <v>100</v>
       </c>
@@ -6608,7 +6702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B38" s="7" t="s">
         <v>103</v>
       </c>
@@ -6628,7 +6722,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B39" s="7" t="s">
         <v>106</v>
       </c>
@@ -6648,7 +6742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B40" s="7" t="s">
         <v>110</v>
       </c>
@@ -6668,7 +6762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B41" s="7" t="s">
         <v>113</v>
       </c>
@@ -6688,7 +6782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B42" s="7" t="s">
         <v>116</v>
       </c>
@@ -6708,7 +6802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B43" s="7" t="s">
         <v>119</v>
       </c>
@@ -6728,7 +6822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B44" s="7" t="s">
         <v>122</v>
       </c>
@@ -6748,7 +6842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B45" s="7" t="s">
         <v>125</v>
       </c>
@@ -6768,7 +6862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B46" s="7" t="s">
         <v>128</v>
       </c>
@@ -6788,7 +6882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B47" s="7" t="s">
         <v>131</v>
       </c>
@@ -6808,7 +6902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B48" s="7" t="s">
         <v>134</v>
       </c>
@@ -6828,7 +6922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B49" s="7" t="s">
         <v>137</v>
       </c>
@@ -6848,7 +6942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B50" s="7" t="s">
         <v>140</v>
       </c>
@@ -6868,7 +6962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B51" s="7" t="s">
         <v>143</v>
       </c>
@@ -6888,7 +6982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B52" s="7" t="s">
         <v>146</v>
       </c>
@@ -6908,7 +7002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B53" s="7" t="s">
         <v>149</v>
       </c>
@@ -6928,12 +7022,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B54" s="7">
-        <v>861612.0</v>
+        <v>861612</v>
       </c>
       <c r="C54" s="7">
-        <v>2.0760235E7</v>
+        <v>20760235</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>152</v>
@@ -6942,13 +7036,13 @@
         <v>33</v>
       </c>
       <c r="F54" s="7">
-        <v>2.0760235E7</v>
+        <v>20760235</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B55" s="7" t="s">
         <v>153</v>
       </c>
@@ -6968,7 +7062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B56" s="7" t="s">
         <v>156</v>
       </c>
@@ -6988,7 +7082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B57" s="7" t="s">
         <v>159</v>
       </c>
@@ -7008,9 +7102,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B58" s="7">
-        <v>2448.0</v>
+        <v>2448</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>162</v>
@@ -7028,7 +7122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B59" s="7" t="s">
         <v>164</v>
       </c>
@@ -7048,7 +7142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B60" s="7" t="s">
         <v>167</v>
       </c>
@@ -7068,7 +7162,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B61" s="7" t="s">
         <v>170</v>
       </c>
@@ -7088,7 +7182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B62" s="7" t="s">
         <v>173</v>
       </c>
@@ -7108,12 +7202,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B63" s="7">
-        <v>801152.0</v>
+        <v>801152</v>
       </c>
       <c r="C63" s="7">
-        <v>2.2195464E7</v>
+        <v>22195464</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>176</v>
@@ -7122,13 +7216,13 @@
         <v>33</v>
       </c>
       <c r="F63" s="7">
-        <v>2.2195464E7</v>
+        <v>22195464</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B64" s="7" t="s">
         <v>177</v>
       </c>
@@ -7148,7 +7242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B65" s="7" t="s">
         <v>180</v>
       </c>
@@ -7168,7 +7262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B66" s="7" t="s">
         <v>183</v>
       </c>
@@ -7188,7 +7282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B67" s="7" t="s">
         <v>186</v>
       </c>
@@ -7208,7 +7302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C68" s="7" t="s">
         <v>189</v>
       </c>
@@ -7225,7 +7319,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B69" s="7" t="s">
         <v>191</v>
       </c>
@@ -7245,7 +7339,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B70" s="7" t="s">
         <v>194</v>
       </c>
@@ -7265,7 +7359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C71" s="7" t="s">
         <v>197</v>
       </c>
@@ -7282,7 +7376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B72" s="7" t="s">
         <v>199</v>
       </c>
@@ -7302,7 +7396,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B73" s="7" t="s">
         <v>202</v>
       </c>
@@ -7322,12 +7416,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B74" s="7">
-        <v>880866.0</v>
+        <v>880866</v>
       </c>
       <c r="C74" s="7">
-        <v>2.1460409E7</v>
+        <v>21460409</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>205</v>
@@ -7336,18 +7430,18 @@
         <v>33</v>
       </c>
       <c r="F74" s="7">
-        <v>2.1460409E7</v>
+        <v>21460409</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B75" s="7">
-        <v>880867.0</v>
+        <v>880867</v>
       </c>
       <c r="C75" s="7">
-        <v>2.1556636E7</v>
+        <v>21556636</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>205</v>
@@ -7356,18 +7450,18 @@
         <v>33</v>
       </c>
       <c r="F75" s="7">
-        <v>2.1556636E7</v>
+        <v>21556636</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B76" s="7">
-        <v>880868.0</v>
+        <v>880868</v>
       </c>
       <c r="C76" s="7">
-        <v>2.1556637E7</v>
+        <v>21556637</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>206</v>
@@ -7376,13 +7470,13 @@
         <v>33</v>
       </c>
       <c r="F76" s="7">
-        <v>2.1556637E7</v>
+        <v>21556637</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B77" s="7" t="s">
         <v>207</v>
       </c>
@@ -7402,7 +7496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B78" s="7" t="s">
         <v>210</v>
       </c>
@@ -7422,7 +7516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B79" s="7" t="s">
         <v>212</v>
       </c>
@@ -7442,9 +7536,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B80" s="7">
-        <v>803950.0</v>
+        <v>803950</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>215</v>
@@ -7462,9 +7556,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B81" s="7">
-        <v>803949.0</v>
+        <v>803949</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>217</v>
@@ -7482,7 +7576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B82" s="7" t="s">
         <v>219</v>
       </c>
@@ -7502,7 +7596,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B83" s="7" t="s">
         <v>222</v>
       </c>
@@ -7522,9 +7616,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B84" s="7">
-        <v>803948.0</v>
+        <v>803948</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>225</v>
@@ -7542,9 +7636,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B85" s="7">
-        <v>803947.0</v>
+        <v>803947</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>227</v>
@@ -7562,7 +7656,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B86" s="7" t="s">
         <v>229</v>
       </c>
@@ -7582,7 +7676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B87" s="7" t="s">
         <v>232</v>
       </c>
@@ -7602,9 +7696,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B88" s="7">
-        <v>805025.0</v>
+        <v>805025</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>235</v>
@@ -7622,9 +7716,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B89" s="7">
-        <v>804042.0</v>
+        <v>804042</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>237</v>
@@ -7642,9 +7736,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B90" s="7">
-        <v>804153.0</v>
+        <v>804153</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>239</v>
@@ -7662,7 +7756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B91" s="7" t="s">
         <v>241</v>
       </c>
@@ -7682,7 +7776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B92" s="7" t="s">
         <v>244</v>
       </c>
@@ -7702,7 +7796,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B93" s="7" t="s">
         <v>247</v>
       </c>
@@ -7722,7 +7816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B94" s="7" t="s">
         <v>250</v>
       </c>
@@ -7742,7 +7836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B95" s="7" t="s">
         <v>253</v>
       </c>
@@ -7762,7 +7856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B96" s="7" t="s">
         <v>256</v>
       </c>
@@ -7782,7 +7876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B97" s="7" t="s">
         <v>259</v>
       </c>
@@ -7802,7 +7896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B98" s="7" t="s">
         <v>262</v>
       </c>
@@ -7822,7 +7916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B99" s="7" t="s">
         <v>264</v>
       </c>
@@ -7842,7 +7936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B100" s="7" t="s">
         <v>267</v>
       </c>
@@ -7862,7 +7956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B101" s="7" t="s">
         <v>270</v>
       </c>
@@ -7882,7 +7976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B102" s="7" t="s">
         <v>273</v>
       </c>
@@ -7902,7 +7996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B103" s="7" t="s">
         <v>276</v>
       </c>
@@ -7922,7 +8016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B104" s="7" t="s">
         <v>279</v>
       </c>
@@ -7942,7 +8036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B105" s="7" t="s">
         <v>282</v>
       </c>
@@ -7962,7 +8056,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B106" s="7" t="s">
         <v>285</v>
       </c>
@@ -7982,7 +8076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B107" s="7" t="s">
         <v>288</v>
       </c>
@@ -8002,7 +8096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B108" s="7" t="s">
         <v>291</v>
       </c>
@@ -8022,9 +8116,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B109" s="7">
-        <v>806778.0</v>
+        <v>806778</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>294</v>
@@ -8042,7 +8136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B110" s="7" t="s">
         <v>295</v>
       </c>
@@ -8062,7 +8156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B111" s="7" t="s">
         <v>298</v>
       </c>
@@ -8082,7 +8176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B112" s="7" t="s">
         <v>301</v>
       </c>
@@ -8102,7 +8196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B113" s="7" t="s">
         <v>304</v>
       </c>
@@ -8122,7 +8216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B114" s="7" t="s">
         <v>307</v>
       </c>
@@ -8142,7 +8236,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B115" s="7" t="s">
         <v>310</v>
       </c>
@@ -8162,7 +8256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B116" s="7" t="s">
         <v>313</v>
       </c>
@@ -8182,9 +8276,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B117" s="7">
-        <v>831013.0</v>
+        <v>831013</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>316</v>
@@ -8202,9 +8296,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B118" s="7">
-        <v>804323.0</v>
+        <v>804323</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>318</v>
@@ -8222,9 +8316,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B119" s="7">
-        <v>803972.0</v>
+        <v>803972</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>320</v>
@@ -8242,7 +8336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B120" s="7" t="s">
         <v>322</v>
       </c>
@@ -8262,7 +8356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B121" s="7" t="s">
         <v>325</v>
       </c>
@@ -8282,7 +8376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B122" s="7" t="s">
         <v>328</v>
       </c>
@@ -8302,7 +8396,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B123" s="7" t="s">
         <v>331</v>
       </c>
@@ -8322,12 +8416,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B124" s="7" t="s">
         <v>334</v>
       </c>
       <c r="C124" s="7">
-        <v>2.1565469E7</v>
+        <v>21565469</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>335</v>
@@ -8336,18 +8430,18 @@
         <v>33</v>
       </c>
       <c r="F124" s="7">
-        <v>2.1565469E7</v>
+        <v>21565469</v>
       </c>
       <c r="G124" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B125" s="7" t="s">
         <v>336</v>
       </c>
       <c r="C125" s="7">
-        <v>7.3139548E8</v>
+        <v>731395480</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>337</v>
@@ -8356,13 +8450,13 @@
         <v>67</v>
       </c>
       <c r="F125" s="7">
-        <v>7.3139548E8</v>
+        <v>731395480</v>
       </c>
       <c r="G125" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B126" s="7" t="s">
         <v>338</v>
       </c>
@@ -8382,7 +8476,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B127" s="7" t="s">
         <v>341</v>
       </c>
@@ -8402,7 +8496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B128" s="7" t="s">
         <v>344</v>
       </c>
@@ -8422,7 +8516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B129" s="7" t="s">
         <v>347</v>
       </c>
@@ -8442,7 +8536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B130" s="7" t="s">
         <v>350</v>
       </c>
@@ -8462,7 +8556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B131" s="7" t="s">
         <v>353</v>
       </c>
@@ -8482,7 +8576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B132" s="7" t="s">
         <v>355</v>
       </c>
@@ -8502,7 +8596,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B133" s="7" t="s">
         <v>357</v>
       </c>
@@ -8522,7 +8616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B134" s="7" t="s">
         <v>359</v>
       </c>
@@ -8542,7 +8636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B135" s="7" t="s">
         <v>361</v>
       </c>
@@ -8562,7 +8656,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B136" s="7" t="s">
         <v>363</v>
       </c>
@@ -8582,7 +8676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B137" s="7" t="s">
         <v>365</v>
       </c>
@@ -8602,7 +8696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B138" s="7" t="s">
         <v>367</v>
       </c>
@@ -8622,7 +8716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B139" s="7" t="s">
         <v>370</v>
       </c>
@@ -8642,7 +8736,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B140" s="7" t="s">
         <v>373</v>
       </c>
@@ -8662,7 +8756,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B141" s="7" t="s">
         <v>376</v>
       </c>
@@ -8682,7 +8776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B142" s="7" t="s">
         <v>379</v>
       </c>
@@ -8702,7 +8796,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B143" s="7" t="s">
         <v>382</v>
       </c>
@@ -8722,7 +8816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B144" s="7" t="s">
         <v>385</v>
       </c>
@@ -8742,7 +8836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B145" s="7" t="s">
         <v>388</v>
       </c>
@@ -8762,7 +8856,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B146" s="7" t="s">
         <v>391</v>
       </c>
@@ -8782,7 +8876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B147" s="7" t="s">
         <v>394</v>
       </c>
@@ -8802,7 +8896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B148" s="7" t="s">
         <v>397</v>
       </c>
@@ -8822,7 +8916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B149" s="7" t="s">
         <v>400</v>
       </c>
@@ -8842,7 +8936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B150" s="7" t="s">
         <v>403</v>
       </c>
@@ -8862,7 +8956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B151" s="7" t="s">
         <v>406</v>
       </c>
@@ -8882,7 +8976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B152" s="7" t="s">
         <v>409</v>
       </c>
@@ -8902,7 +8996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B153" s="7" t="s">
         <v>412</v>
       </c>
@@ -8922,7 +9016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B154" s="7" t="s">
         <v>415</v>
       </c>
@@ -8942,7 +9036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B155" s="7" t="s">
         <v>418</v>
       </c>
@@ -8962,9 +9056,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B156" s="7">
-        <v>803924.0</v>
+        <v>803924</v>
       </c>
       <c r="C156" s="7" t="s">
         <v>421</v>
@@ -8982,7 +9076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B157" s="7" t="s">
         <v>423</v>
       </c>
@@ -9002,7 +9096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B158" s="7" t="s">
         <v>426</v>
       </c>
@@ -9022,7 +9116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B159" s="7" t="s">
         <v>429</v>
       </c>
@@ -9042,7 +9136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B160" s="7" t="s">
         <v>431</v>
       </c>
@@ -9062,7 +9156,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B161" s="7" t="s">
         <v>433</v>
       </c>
@@ -9082,7 +9176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B162" s="7" t="s">
         <v>435</v>
       </c>
@@ -9102,7 +9196,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B163" s="7" t="s">
         <v>438</v>
       </c>
@@ -9122,7 +9216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B164" s="7" t="s">
         <v>441</v>
       </c>
@@ -9142,9 +9236,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B165" s="7">
-        <v>804140.0</v>
+        <v>804140</v>
       </c>
       <c r="C165" s="7" t="s">
         <v>444</v>
@@ -9162,9 +9256,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B166" s="7">
-        <v>804144.0</v>
+        <v>804144</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>446</v>
@@ -9182,9 +9276,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B167" s="7">
-        <v>804143.0</v>
+        <v>804143</v>
       </c>
       <c r="C167" s="7" t="s">
         <v>448</v>
@@ -9202,9 +9296,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B168" s="7">
-        <v>804141.0</v>
+        <v>804141</v>
       </c>
       <c r="C168" s="7" t="s">
         <v>450</v>
@@ -9222,9 +9316,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B169" s="7">
-        <v>804138.0</v>
+        <v>804138</v>
       </c>
       <c r="C169" s="7" t="s">
         <v>452</v>
@@ -9242,7 +9336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B170" s="7" t="s">
         <v>454</v>
       </c>
@@ -9262,9 +9356,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B171" s="7">
-        <v>804142.0</v>
+        <v>804142</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>457</v>
@@ -9282,9 +9376,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B172" s="7">
-        <v>804139.0</v>
+        <v>804139</v>
       </c>
       <c r="C172" s="7" t="s">
         <v>459</v>
@@ -9302,9 +9396,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B173" s="7">
-        <v>803998.0</v>
+        <v>803998</v>
       </c>
       <c r="C173" s="7" t="s">
         <v>461</v>
@@ -9322,9 +9416,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B174" s="7">
-        <v>804152.0</v>
+        <v>804152</v>
       </c>
       <c r="C174" s="7" t="s">
         <v>463</v>
@@ -9342,7 +9436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C175" s="7" t="s">
         <v>465</v>
       </c>
@@ -9359,7 +9453,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B176" s="7" t="s">
         <v>467</v>
       </c>
@@ -9379,7 +9473,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B177" s="7" t="s">
         <v>470</v>
       </c>
@@ -9399,9 +9493,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B178" s="7">
-        <v>804145.0</v>
+        <v>804145</v>
       </c>
       <c r="C178" s="7" t="s">
         <v>473</v>
@@ -9419,9 +9513,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B179" s="7">
-        <v>804146.0</v>
+        <v>804146</v>
       </c>
       <c r="C179" s="7" t="s">
         <v>475</v>
@@ -9439,9 +9533,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B180" s="7">
-        <v>803407.0</v>
+        <v>803407</v>
       </c>
       <c r="C180" s="7" t="s">
         <v>477</v>
@@ -9459,7 +9553,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B181" s="7" t="s">
         <v>479</v>
       </c>
@@ -9479,7 +9573,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B182" s="7" t="s">
         <v>482</v>
       </c>
@@ -9499,7 +9593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B183" s="7" t="s">
         <v>485</v>
       </c>
@@ -9519,7 +9613,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B184" s="7" t="s">
         <v>488</v>
       </c>
@@ -9539,7 +9633,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B185" s="7" t="s">
         <v>491</v>
       </c>
@@ -9559,7 +9653,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B186" s="7" t="s">
         <v>494</v>
       </c>
@@ -9579,7 +9673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B187" s="7" t="s">
         <v>497</v>
       </c>
@@ -9599,7 +9693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B188" s="7" t="s">
         <v>500</v>
       </c>
@@ -9619,12 +9713,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B189" s="7">
-        <v>831060.0</v>
+        <v>831060</v>
       </c>
       <c r="C189" s="7">
-        <v>2.1409435E7</v>
+        <v>21409435</v>
       </c>
       <c r="D189" s="7" t="s">
         <v>503</v>
@@ -9633,13 +9727,13 @@
         <v>33</v>
       </c>
       <c r="F189" s="7">
-        <v>2.1409435E7</v>
+        <v>21409435</v>
       </c>
       <c r="G189" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B190" s="7" t="s">
         <v>504</v>
       </c>
@@ -9659,7 +9753,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B191" s="7" t="s">
         <v>507</v>
       </c>
@@ -9679,7 +9773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B192" s="7" t="s">
         <v>510</v>
       </c>
@@ -9699,7 +9793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B193" s="7" t="s">
         <v>513</v>
       </c>
@@ -9719,7 +9813,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B194" s="7" t="s">
         <v>516</v>
       </c>
@@ -9739,12 +9833,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B195" s="7" t="s">
         <v>519</v>
       </c>
       <c r="C195" s="7">
-        <v>318417.0</v>
+        <v>318417</v>
       </c>
       <c r="D195" s="7" t="s">
         <v>520</v>
@@ -9753,18 +9847,18 @@
         <v>33</v>
       </c>
       <c r="F195" s="7">
-        <v>318417.0</v>
+        <v>318417</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B196" s="7">
-        <v>803914.0</v>
+        <v>803914</v>
       </c>
       <c r="C196" s="7">
-        <v>318417.0</v>
+        <v>318417</v>
       </c>
       <c r="D196" s="7" t="s">
         <v>521</v>
@@ -9773,13 +9867,13 @@
         <v>33</v>
       </c>
       <c r="F196" s="7">
-        <v>318417.0</v>
+        <v>318417</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B197" s="7" t="s">
         <v>522</v>
       </c>
@@ -9799,9 +9893,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B198" s="7">
-        <v>806860.0</v>
+        <v>806860</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>525</v>
@@ -9819,7 +9913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B199" s="7" t="s">
         <v>527</v>
       </c>
@@ -9839,7 +9933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B200" s="7" t="s">
         <v>530</v>
       </c>
@@ -9859,7 +9953,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B201" s="7" t="s">
         <v>533</v>
       </c>
@@ -9879,7 +9973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B202" s="7" t="s">
         <v>536</v>
       </c>
@@ -9899,7 +9993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B203" s="7" t="s">
         <v>539</v>
       </c>
@@ -9919,7 +10013,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B204" s="7" t="s">
         <v>542</v>
       </c>
@@ -9939,7 +10033,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B205" s="7" t="s">
         <v>545</v>
       </c>
@@ -9959,7 +10053,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B206" s="7" t="s">
         <v>548</v>
       </c>
@@ -9979,7 +10073,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B207" s="7" t="s">
         <v>551</v>
       </c>
@@ -9999,7 +10093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B208" s="7" t="s">
         <v>554</v>
       </c>
@@ -10019,9 +10113,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B209" s="7">
-        <v>840153.0</v>
+        <v>840153</v>
       </c>
       <c r="C209" s="7" t="s">
         <v>557</v>
@@ -10039,7 +10133,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B210" s="7" t="s">
         <v>559</v>
       </c>
@@ -10059,7 +10153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B211" s="7" t="s">
         <v>562</v>
       </c>
@@ -10079,9 +10173,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B212" s="7">
-        <v>840154.0</v>
+        <v>840154</v>
       </c>
       <c r="C212" s="7" t="s">
         <v>565</v>
@@ -10099,7 +10193,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B213" s="7" t="s">
         <v>567</v>
       </c>
@@ -10119,9 +10213,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B214" s="7">
-        <v>803933.0</v>
+        <v>803933</v>
       </c>
       <c r="C214" s="7" t="s">
         <v>570</v>
@@ -10139,9 +10233,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B215" s="7">
-        <v>803932.0</v>
+        <v>803932</v>
       </c>
       <c r="C215" s="7" t="s">
         <v>572</v>
@@ -10159,7 +10253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B216" s="7" t="s">
         <v>574</v>
       </c>
@@ -10179,9 +10273,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B217" s="7">
-        <v>803881.0</v>
+        <v>803881</v>
       </c>
       <c r="C217" s="7" t="s">
         <v>577</v>
@@ -10199,7 +10293,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B218" s="7" t="s">
         <v>579</v>
       </c>
@@ -10219,12 +10313,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B219" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C219" s="7">
-        <v>8.2720309E7</v>
+        <v>82720309</v>
       </c>
       <c r="D219" s="7" t="s">
         <v>583</v>
@@ -10233,15 +10327,15 @@
         <v>67</v>
       </c>
       <c r="F219" s="7">
-        <v>8.2720309E7</v>
+        <v>82720309</v>
       </c>
       <c r="G219" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B220" s="7">
-        <v>804013.0</v>
+        <v>804013</v>
       </c>
       <c r="C220" s="7" t="s">
         <v>584</v>
@@ -10259,7 +10353,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B221" s="7" t="s">
         <v>586</v>
       </c>
@@ -10279,7 +10373,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B222" s="7" t="s">
         <v>589</v>
       </c>
@@ -10299,12 +10393,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B223" s="7">
-        <v>871100.0</v>
+        <v>871100</v>
       </c>
       <c r="C223" s="7">
-        <v>2.0580558E7</v>
+        <v>20580558</v>
       </c>
       <c r="D223" s="7" t="s">
         <v>592</v>
@@ -10313,13 +10407,13 @@
         <v>33</v>
       </c>
       <c r="F223" s="7">
-        <v>2.0580558E7</v>
+        <v>20580558</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B224" s="7" t="s">
         <v>593</v>
       </c>
@@ -10339,7 +10433,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B225" s="7" t="s">
         <v>596</v>
       </c>
@@ -10359,7 +10453,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B226" s="7" t="s">
         <v>599</v>
       </c>
@@ -10379,7 +10473,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B227" s="7" t="s">
         <v>602</v>
       </c>
@@ -10399,7 +10493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B228" s="7" t="s">
         <v>605</v>
       </c>
@@ -10419,7 +10513,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B229" s="7" t="s">
         <v>608</v>
       </c>
@@ -10439,7 +10533,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B230" s="7" t="s">
         <v>611</v>
       </c>
@@ -10459,7 +10553,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B231" s="7" t="s">
         <v>614</v>
       </c>
@@ -10479,9 +10573,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B232" s="7">
-        <v>803710.0</v>
+        <v>803710</v>
       </c>
       <c r="C232" s="7" t="s">
         <v>617</v>
@@ -10499,7 +10593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B233" s="7" t="s">
         <v>619</v>
       </c>
@@ -10519,7 +10613,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B234" s="7" t="s">
         <v>622</v>
       </c>
@@ -10539,7 +10633,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B235" s="7" t="s">
         <v>625</v>
       </c>
@@ -10559,7 +10653,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B236" s="7" t="s">
         <v>628</v>
       </c>
@@ -10579,12 +10673,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B237" s="7">
-        <v>836011.0</v>
+        <v>836011</v>
       </c>
       <c r="C237" s="7">
-        <v>2.0430678E7</v>
+        <v>20430678</v>
       </c>
       <c r="D237" s="7" t="s">
         <v>631</v>
@@ -10593,13 +10687,13 @@
         <v>33</v>
       </c>
       <c r="F237" s="7">
-        <v>2.0430678E7</v>
+        <v>20430678</v>
       </c>
       <c r="G237" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B238" s="7" t="s">
         <v>632</v>
       </c>
@@ -10619,7 +10713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B239" s="7" t="s">
         <v>635</v>
       </c>
@@ -10639,7 +10733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B240" s="7" t="s">
         <v>638</v>
       </c>
@@ -10659,7 +10753,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B241" s="7" t="s">
         <v>641</v>
       </c>
@@ -10679,7 +10773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B242" s="7" t="s">
         <v>644</v>
       </c>
@@ -10699,9 +10793,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B243" s="7">
-        <v>803707.0</v>
+        <v>803707</v>
       </c>
       <c r="C243" s="7" t="s">
         <v>647</v>
@@ -10719,7 +10813,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B244" s="7" t="s">
         <v>649</v>
       </c>
@@ -10739,7 +10833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B245" s="7" t="s">
         <v>652</v>
       </c>
@@ -10759,7 +10853,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B246" s="7" t="s">
         <v>655</v>
       </c>
@@ -10779,7 +10873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B247" s="7" t="s">
         <v>658</v>
       </c>
@@ -10799,7 +10893,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B248" s="7" t="s">
         <v>661</v>
       </c>
@@ -10819,7 +10913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B249" s="7" t="s">
         <v>664</v>
       </c>
@@ -10839,7 +10933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B250" s="7" t="s">
         <v>667</v>
       </c>
@@ -10859,7 +10953,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B251" s="7" t="s">
         <v>670</v>
       </c>
@@ -10879,7 +10973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B252" s="7" t="s">
         <v>673</v>
       </c>
@@ -10899,7 +10993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B253" s="7" t="s">
         <v>676</v>
       </c>
@@ -10919,7 +11013,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B254" s="7" t="s">
         <v>679</v>
       </c>
@@ -10939,7 +11033,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C255" s="7" t="s">
         <v>680</v>
       </c>
@@ -10956,7 +11050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B256" s="7" t="s">
         <v>683</v>
       </c>
@@ -10976,7 +11070,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B257" s="7" t="s">
         <v>686</v>
       </c>
@@ -10996,7 +11090,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B258" s="7" t="s">
         <v>688</v>
       </c>
@@ -11016,7 +11110,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B259" s="7" t="s">
         <v>691</v>
       </c>
@@ -11036,7 +11130,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B260" s="7" t="s">
         <v>694</v>
       </c>
@@ -11056,7 +11150,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B261" s="7" t="s">
         <v>697</v>
       </c>
@@ -11076,9 +11170,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B262" s="7">
-        <v>804295.0</v>
+        <v>804295</v>
       </c>
       <c r="C262" s="7" t="s">
         <v>700</v>
@@ -11096,7 +11190,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B263" s="7" t="s">
         <v>702</v>
       </c>
@@ -11116,7 +11210,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B264" s="7" t="s">
         <v>705</v>
       </c>
@@ -11136,7 +11230,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B265" s="7" t="s">
         <v>708</v>
       </c>
@@ -11156,7 +11250,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B266" s="7" t="s">
         <v>711</v>
       </c>
@@ -11176,7 +11270,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B267" s="7" t="s">
         <v>714</v>
       </c>
@@ -11196,7 +11290,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B268" s="7" t="s">
         <v>717</v>
       </c>
@@ -11216,9 +11310,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B269" s="7">
-        <v>804125.0</v>
+        <v>804125</v>
       </c>
       <c r="C269" s="7" t="s">
         <v>720</v>
@@ -11236,7 +11330,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B270" s="7" t="s">
         <v>722</v>
       </c>
@@ -11256,7 +11350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B271" s="7" t="s">
         <v>725</v>
       </c>
@@ -11276,7 +11370,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B272" s="7" t="s">
         <v>728</v>
       </c>
@@ -11296,7 +11390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B273" s="7" t="s">
         <v>731</v>
       </c>
@@ -11316,7 +11410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B274" s="7" t="s">
         <v>734</v>
       </c>
@@ -11336,7 +11430,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B275" s="7" t="s">
         <v>737</v>
       </c>
@@ -11356,7 +11450,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B276" s="7" t="s">
         <v>739</v>
       </c>
@@ -11376,7 +11470,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B277" s="7" t="s">
         <v>742</v>
       </c>
@@ -11396,7 +11490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B278" s="7" t="s">
         <v>745</v>
       </c>
@@ -11416,7 +11510,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B279" s="7" t="s">
         <v>748</v>
       </c>
@@ -11436,7 +11530,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B280" s="7" t="s">
         <v>751</v>
       </c>
@@ -11456,7 +11550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B281" s="7" t="s">
         <v>754</v>
       </c>
@@ -11476,9 +11570,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B282" s="7">
-        <v>806831.0</v>
+        <v>806831</v>
       </c>
       <c r="C282" s="7" t="s">
         <v>757</v>
@@ -11496,9 +11590,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B283" s="7">
-        <v>806774.0</v>
+        <v>806774</v>
       </c>
       <c r="C283" s="7" t="s">
         <v>759</v>
@@ -11516,9 +11610,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B284" s="7">
-        <v>806775.0</v>
+        <v>806775</v>
       </c>
       <c r="C284" s="7" t="s">
         <v>761</v>
@@ -11536,9 +11630,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B285" s="7">
-        <v>806811.0</v>
+        <v>806811</v>
       </c>
       <c r="C285" s="7" t="s">
         <v>762</v>
@@ -11556,7 +11650,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B286" s="7" t="s">
         <v>763</v>
       </c>
@@ -11576,7 +11670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B287" s="7" t="s">
         <v>765</v>
       </c>
@@ -11596,7 +11690,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B288" s="7" t="s">
         <v>767</v>
       </c>
@@ -11616,7 +11710,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B289" s="7" t="s">
         <v>769</v>
       </c>
@@ -11636,7 +11730,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B290" s="7" t="s">
         <v>771</v>
       </c>
@@ -11656,9 +11750,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B291" s="7">
-        <v>806776.0</v>
+        <v>806776</v>
       </c>
       <c r="C291" s="7" t="s">
         <v>773</v>
@@ -11676,9 +11770,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B292" s="7">
-        <v>806810.0</v>
+        <v>806810</v>
       </c>
       <c r="C292" s="7" t="s">
         <v>775</v>
@@ -11696,9 +11790,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B293" s="7">
-        <v>806828.0</v>
+        <v>806828</v>
       </c>
       <c r="C293" s="7" t="s">
         <v>776</v>
@@ -11716,9 +11810,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B294" s="7">
-        <v>806829.0</v>
+        <v>806829</v>
       </c>
       <c r="C294" s="7" t="s">
         <v>777</v>
@@ -11736,9 +11830,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B295" s="7">
-        <v>806830.0</v>
+        <v>806830</v>
       </c>
       <c r="C295" s="7" t="s">
         <v>778</v>
@@ -11756,9 +11850,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B296" s="7">
-        <v>806832.0</v>
+        <v>806832</v>
       </c>
       <c r="C296" s="7" t="s">
         <v>779</v>
@@ -11776,7 +11870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B297" s="7" t="s">
         <v>780</v>
       </c>
@@ -11796,7 +11890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B298" s="7" t="s">
         <v>782</v>
       </c>
@@ -11816,7 +11910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B299" s="7" t="s">
         <v>784</v>
       </c>
@@ -11836,7 +11930,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B300" s="7" t="s">
         <v>786</v>
       </c>
@@ -11856,7 +11950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B301" s="7" t="s">
         <v>788</v>
       </c>
@@ -11876,7 +11970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B302" s="7" t="s">
         <v>790</v>
       </c>
@@ -11896,7 +11990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B303" s="7" t="s">
         <v>792</v>
       </c>
@@ -11916,7 +12010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B304" s="7" t="s">
         <v>794</v>
       </c>
@@ -11936,7 +12030,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B305" s="7" t="s">
         <v>796</v>
       </c>
@@ -11956,7 +12050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B306" s="7" t="s">
         <v>798</v>
       </c>
@@ -11976,12 +12070,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B307" s="7" t="s">
         <v>801</v>
       </c>
       <c r="C307" s="7">
-        <v>2.163636E7</v>
+        <v>21636360</v>
       </c>
       <c r="D307" s="7" t="s">
         <v>802</v>
@@ -11990,13 +12084,13 @@
         <v>74</v>
       </c>
       <c r="F307" s="7">
-        <v>2.163636E7</v>
+        <v>21636360</v>
       </c>
       <c r="G307" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B308" s="7" t="s">
         <v>803</v>
       </c>
@@ -12016,7 +12110,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B309" s="7" t="s">
         <v>805</v>
       </c>
@@ -12036,9 +12130,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B310" s="7">
-        <v>806731.0</v>
+        <v>806731</v>
       </c>
       <c r="C310" s="7" t="s">
         <v>808</v>
@@ -12056,7 +12150,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B311" s="7" t="s">
         <v>810</v>
       </c>
@@ -12076,7 +12170,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B312" s="7" t="s">
         <v>812</v>
       </c>
@@ -12096,7 +12190,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B313" s="7" t="s">
         <v>815</v>
       </c>
@@ -12116,7 +12210,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B314" s="7" t="s">
         <v>818</v>
       </c>
@@ -12136,7 +12230,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B315" s="7" t="s">
         <v>821</v>
       </c>
@@ -12156,9 +12250,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B316" s="7">
-        <v>806800.0</v>
+        <v>806800</v>
       </c>
       <c r="C316" s="7" t="s">
         <v>824</v>
@@ -12176,9 +12270,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B317" s="7">
-        <v>806801.0</v>
+        <v>806801</v>
       </c>
       <c r="C317" s="7" t="s">
         <v>826</v>
@@ -12196,7 +12290,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B318" s="7" t="s">
         <v>827</v>
       </c>
@@ -12216,9 +12310,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B319" s="7">
-        <v>808061.0</v>
+        <v>808061</v>
       </c>
       <c r="C319" s="7" t="s">
         <v>830</v>
@@ -12236,7 +12330,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B320" s="7" t="s">
         <v>832</v>
       </c>
@@ -12256,7 +12350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B321" s="7" t="s">
         <v>835</v>
       </c>
@@ -12276,9 +12370,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B322" s="7">
-        <v>808060.0</v>
+        <v>808060</v>
       </c>
       <c r="C322" s="7" t="s">
         <v>838</v>
@@ -12296,7 +12390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B323" s="7" t="s">
         <v>840</v>
       </c>
@@ -12316,7 +12410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B324" s="7" t="s">
         <v>843</v>
       </c>
@@ -12336,9 +12430,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B325" s="7">
-        <v>2532.0</v>
+        <v>2532</v>
       </c>
       <c r="C325" s="7" t="s">
         <v>846</v>
@@ -12356,7 +12450,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B326" s="7" t="s">
         <v>848</v>
       </c>
@@ -12376,7 +12470,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B327" s="7" t="s">
         <v>851</v>
       </c>
@@ -12396,7 +12490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B328" s="7" t="s">
         <v>854</v>
       </c>
@@ -12416,12 +12510,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B329" s="7">
-        <v>880896.0</v>
+        <v>880896</v>
       </c>
       <c r="C329" s="7">
-        <v>2.1753149E7</v>
+        <v>21753149</v>
       </c>
       <c r="D329" s="7" t="s">
         <v>857</v>
@@ -12430,13 +12524,13 @@
         <v>33</v>
       </c>
       <c r="F329" s="7">
-        <v>2.1753149E7</v>
+        <v>21753149</v>
       </c>
       <c r="G329" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B330" s="7" t="s">
         <v>858</v>
       </c>
@@ -12456,12 +12550,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B331" s="7">
-        <v>803722.0</v>
+        <v>803722</v>
       </c>
       <c r="C331" s="7">
-        <v>1.108707001E9</v>
+        <v>1108707001</v>
       </c>
       <c r="D331" s="7" t="s">
         <v>861</v>
@@ -12470,13 +12564,13 @@
         <v>17</v>
       </c>
       <c r="F331" s="7">
-        <v>1.108707001E9</v>
+        <v>1108707001</v>
       </c>
       <c r="G331" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B332" s="7" t="s">
         <v>862</v>
       </c>
@@ -12496,7 +12590,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B333" s="7" t="s">
         <v>865</v>
       </c>
@@ -12516,12 +12610,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B334" s="7">
-        <v>804271.0</v>
+        <v>804271</v>
       </c>
       <c r="C334" s="7">
-        <v>2.1338449E7</v>
+        <v>21338449</v>
       </c>
       <c r="D334" s="7" t="s">
         <v>868</v>
@@ -12530,13 +12624,13 @@
         <v>17</v>
       </c>
       <c r="F334" s="7">
-        <v>2.1338449E7</v>
+        <v>21338449</v>
       </c>
       <c r="G334" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B335" s="7" t="s">
         <v>869</v>
       </c>
@@ -12556,9 +12650,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B336" s="7">
-        <v>804259.0</v>
+        <v>804259</v>
       </c>
       <c r="C336" s="7" t="s">
         <v>872</v>
@@ -12576,7 +12670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B337" s="7" t="s">
         <v>874</v>
       </c>
@@ -12596,9 +12690,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B338" s="7">
-        <v>960150.0</v>
+        <v>960150</v>
       </c>
       <c r="C338" s="7" t="s">
         <v>877</v>
@@ -12616,9 +12710,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C339" s="7">
-        <v>2.3367142E7</v>
+        <v>23367142</v>
       </c>
       <c r="D339" s="7" t="s">
         <v>879</v>
@@ -12627,15 +12721,15 @@
         <v>67</v>
       </c>
       <c r="F339" s="7">
-        <v>2.3367142E7</v>
+        <v>23367142</v>
       </c>
       <c r="G339" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C340" s="7">
-        <v>848977.0</v>
+        <v>848977</v>
       </c>
       <c r="D340" s="7" t="s">
         <v>880</v>
@@ -12644,15 +12738,15 @@
         <v>33</v>
       </c>
       <c r="F340" s="7">
-        <v>848977.0</v>
+        <v>848977</v>
       </c>
       <c r="G340" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C341" s="7">
-        <v>848978.0</v>
+        <v>848978</v>
       </c>
       <c r="D341" s="7" t="s">
         <v>881</v>
@@ -12661,13 +12755,13 @@
         <v>33</v>
       </c>
       <c r="F341" s="7">
-        <v>848978.0</v>
+        <v>848978</v>
       </c>
       <c r="G341" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C342" s="7" t="s">
         <v>882</v>
       </c>
@@ -12684,9 +12778,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="343">
+    <row r="343" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B343" s="7">
-        <v>804022.0</v>
+        <v>804022</v>
       </c>
       <c r="C343" s="7" t="s">
         <v>884</v>
@@ -12704,9 +12798,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B344" s="7">
-        <v>804021.0</v>
+        <v>804021</v>
       </c>
       <c r="C344" s="7" t="s">
         <v>884</v>
@@ -12724,9 +12818,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B345" s="7">
-        <v>804208.0</v>
+        <v>804208</v>
       </c>
       <c r="C345" s="7" t="s">
         <v>887</v>
@@ -12744,12 +12838,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B346" s="7">
-        <v>836018.0</v>
+        <v>836018</v>
       </c>
       <c r="C346" s="7">
-        <v>2.1347078E7</v>
+        <v>21347078</v>
       </c>
       <c r="D346" s="7" t="s">
         <v>889</v>
@@ -12758,13 +12852,13 @@
         <v>33</v>
       </c>
       <c r="F346" s="7">
-        <v>2.1347078E7</v>
+        <v>21347078</v>
       </c>
       <c r="G346" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B347" s="7" t="s">
         <v>890</v>
       </c>
@@ -12784,7 +12878,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B348" s="7" t="s">
         <v>893</v>
       </c>
@@ -12804,12 +12898,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B349" s="7">
-        <v>836020.0</v>
+        <v>836020</v>
       </c>
       <c r="C349" s="7">
-        <v>2.0441481E7</v>
+        <v>20441481</v>
       </c>
       <c r="D349" s="7" t="s">
         <v>896</v>
@@ -12818,13 +12912,13 @@
         <v>33</v>
       </c>
       <c r="F349" s="7">
-        <v>2.0441481E7</v>
+        <v>20441481</v>
       </c>
       <c r="G349" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B350" s="7" t="s">
         <v>897</v>
       </c>
@@ -12844,7 +12938,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B351" s="7" t="s">
         <v>900</v>
       </c>
@@ -12864,7 +12958,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B352" s="7" t="s">
         <v>903</v>
       </c>
@@ -12884,7 +12978,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B353" s="7" t="s">
         <v>906</v>
       </c>
@@ -12904,7 +12998,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354">
+    <row r="354" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B354" s="7" t="s">
         <v>909</v>
       </c>
@@ -12924,7 +13018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="355">
+    <row r="355" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B355" s="7" t="s">
         <v>912</v>
       </c>
@@ -12944,7 +13038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356">
+    <row r="356" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B356" s="7" t="s">
         <v>915</v>
       </c>
@@ -12964,7 +13058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="357">
+    <row r="357" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B357" s="7" t="s">
         <v>918</v>
       </c>
@@ -12984,7 +13078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="358">
+    <row r="358" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B358" s="7" t="s">
         <v>921</v>
       </c>
@@ -13004,7 +13098,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B359" s="7" t="s">
         <v>924</v>
       </c>
@@ -13024,7 +13118,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B360" s="7" t="s">
         <v>927</v>
       </c>
@@ -13044,7 +13138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B361" s="7" t="s">
         <v>930</v>
       </c>
@@ -13064,7 +13158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B362" s="7" t="s">
         <v>933</v>
       </c>
@@ -13084,7 +13178,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B363" s="7" t="s">
         <v>936</v>
       </c>
@@ -13104,7 +13198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B364" s="7" t="s">
         <v>939</v>
       </c>
@@ -13124,7 +13218,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B365" s="7" t="s">
         <v>942</v>
       </c>
@@ -13144,7 +13238,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B366" s="7" t="s">
         <v>945</v>
       </c>
@@ -13164,7 +13258,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B367" s="7" t="s">
         <v>948</v>
       </c>
@@ -13184,7 +13278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B368" s="7" t="s">
         <v>951</v>
       </c>
@@ -13204,7 +13298,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B369" s="7" t="s">
         <v>954</v>
       </c>
@@ -13224,7 +13318,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B370" s="7" t="s">
         <v>957</v>
       </c>
@@ -13244,7 +13338,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B371" s="7" t="s">
         <v>960</v>
       </c>
@@ -13264,7 +13358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372">
+    <row r="372" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B372" s="7" t="s">
         <v>963</v>
       </c>
@@ -13284,7 +13378,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B373" s="7" t="s">
         <v>966</v>
       </c>
@@ -13304,7 +13398,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B374" s="7" t="s">
         <v>969</v>
       </c>
@@ -13324,7 +13418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="375">
+    <row r="375" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B375" s="7" t="s">
         <v>972</v>
       </c>
@@ -13344,7 +13438,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B376" s="7" t="s">
         <v>975</v>
       </c>
@@ -13364,7 +13458,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="377">
+    <row r="377" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B377" s="7" t="s">
         <v>978</v>
       </c>
@@ -13384,7 +13478,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B378" s="7" t="s">
         <v>981</v>
       </c>
@@ -13404,7 +13498,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B379" s="7" t="s">
         <v>984</v>
       </c>
@@ -13424,7 +13518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="380">
+    <row r="380" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B380" s="7" t="s">
         <v>987</v>
       </c>
@@ -13444,7 +13538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="381">
+    <row r="381" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B381" s="7" t="s">
         <v>990</v>
       </c>
@@ -13464,7 +13558,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B382" s="7" t="s">
         <v>992</v>
       </c>
@@ -13484,7 +13578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="383">
+    <row r="383" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B383" s="7" t="s">
         <v>995</v>
       </c>
@@ -13504,7 +13598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="384">
+    <row r="384" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B384" s="7" t="s">
         <v>998</v>
       </c>
@@ -13524,7 +13618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B385" s="7" t="s">
         <v>1001</v>
       </c>
@@ -13544,7 +13638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="386">
+    <row r="386" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B386" s="7" t="s">
         <v>1004</v>
       </c>
@@ -13564,7 +13658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="387">
+    <row r="387" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B387" s="7" t="s">
         <v>981</v>
       </c>
@@ -13584,7 +13678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="388">
+    <row r="388" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B388" s="7" t="s">
         <v>1007</v>
       </c>
@@ -13604,7 +13698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="389">
+    <row r="389" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B389" s="7" t="s">
         <v>1010</v>
       </c>
@@ -13624,7 +13718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B390" s="7" t="s">
         <v>1013</v>
       </c>
@@ -13644,7 +13738,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="391">
+    <row r="391" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B391" s="7" t="s">
         <v>1015</v>
       </c>
@@ -13664,7 +13758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="392">
+    <row r="392" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B392" s="7" t="s">
         <v>1017</v>
       </c>
@@ -13684,7 +13778,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="393">
+    <row r="393" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B393" s="7" t="s">
         <v>1019</v>
       </c>
@@ -13704,7 +13798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="394">
+    <row r="394" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B394" s="7" t="s">
         <v>1022</v>
       </c>
@@ -13721,7 +13815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="395">
+    <row r="395" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B395" s="7" t="s">
         <v>1025</v>
       </c>
@@ -13741,9 +13835,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="396">
+    <row r="396" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B396" s="7">
-        <v>853725.0</v>
+        <v>853725</v>
       </c>
       <c r="C396" s="7" t="s">
         <v>1028</v>
@@ -13761,7 +13855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B397" s="7" t="s">
         <v>1030</v>
       </c>
@@ -13781,7 +13875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="398">
+    <row r="398" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B398" s="7" t="s">
         <v>1033</v>
       </c>
@@ -13801,7 +13895,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B399" s="7" t="s">
         <v>1036</v>
       </c>
@@ -13821,7 +13915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B400" s="7" t="s">
         <v>1039</v>
       </c>
@@ -13841,9 +13935,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="401">
+    <row r="401" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B401" s="7">
-        <v>853708.0</v>
+        <v>853708</v>
       </c>
       <c r="C401" s="7" t="s">
         <v>1042</v>
@@ -13861,12 +13955,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="402">
+    <row r="402" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B402" s="7">
-        <v>853712.0</v>
+        <v>853712</v>
       </c>
       <c r="C402" s="7">
-        <v>2.1746206E7</v>
+        <v>21746206</v>
       </c>
       <c r="D402" s="7" t="s">
         <v>1044</v>
@@ -13875,13 +13969,13 @@
         <v>109</v>
       </c>
       <c r="F402" s="7">
-        <v>2.1746206E7</v>
+        <v>21746206</v>
       </c>
       <c r="G402" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="403">
+    <row r="403" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B403" s="7" t="s">
         <v>1045</v>
       </c>
@@ -13901,7 +13995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="404">
+    <row r="404" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B404" s="7" t="s">
         <v>1048</v>
       </c>
@@ -13921,12 +14015,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="405">
+    <row r="405" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B405" s="7">
-        <v>853709.0</v>
+        <v>853709</v>
       </c>
       <c r="C405" s="7">
-        <v>2.051334E7</v>
+        <v>20513340</v>
       </c>
       <c r="D405" s="7" t="s">
         <v>1051</v>
@@ -13935,13 +14029,13 @@
         <v>109</v>
       </c>
       <c r="F405" s="7">
-        <v>2.051334E7</v>
+        <v>20513340</v>
       </c>
       <c r="G405" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B406" s="7" t="s">
         <v>1052</v>
       </c>
@@ -13961,7 +14055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B407" s="7" t="s">
         <v>1055</v>
       </c>
@@ -13981,7 +14075,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="408">
+    <row r="408" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B408" s="7" t="s">
         <v>1058</v>
       </c>
@@ -14001,7 +14095,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="409">
+    <row r="409" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B409" s="7" t="s">
         <v>1061</v>
       </c>
@@ -14021,9 +14115,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="410">
+    <row r="410" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B410" s="7">
-        <v>803979.0</v>
+        <v>803979</v>
       </c>
       <c r="C410" s="7" t="s">
         <v>1064</v>
@@ -14041,9 +14135,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="411">
+    <row r="411" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B411" s="7">
-        <v>803980.0</v>
+        <v>803980</v>
       </c>
       <c r="C411" s="7" t="s">
         <v>1066</v>
@@ -14061,7 +14155,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="412">
+    <row r="412" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B412" s="7" t="s">
         <v>1068</v>
       </c>
@@ -14081,7 +14175,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B413" s="7" t="s">
         <v>1071</v>
       </c>
@@ -14101,9 +14195,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="414">
+    <row r="414" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B414" s="7">
-        <v>803975.0</v>
+        <v>803975</v>
       </c>
       <c r="C414" s="7" t="s">
         <v>1074</v>
@@ -14121,7 +14215,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="415">
+    <row r="415" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B415" s="7" t="s">
         <v>1076</v>
       </c>
@@ -14141,7 +14235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="416">
+    <row r="416" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B416" s="7" t="s">
         <v>1079</v>
       </c>
@@ -14161,9 +14255,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="417">
+    <row r="417" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B417" s="7">
-        <v>803973.0</v>
+        <v>803973</v>
       </c>
       <c r="C417" s="7" t="s">
         <v>1082</v>
@@ -14181,9 +14275,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B418" s="7">
-        <v>803843.0</v>
+        <v>803843</v>
       </c>
       <c r="C418" s="7" t="s">
         <v>1084</v>
@@ -14201,7 +14295,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="419">
+    <row r="419" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B419" s="7" t="s">
         <v>1086</v>
       </c>
@@ -14221,7 +14315,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="420">
+    <row r="420" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B420" s="7" t="s">
         <v>1089</v>
       </c>
@@ -14241,9 +14335,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="421">
+    <row r="421" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B421" s="7">
-        <v>801100.0</v>
+        <v>801100</v>
       </c>
       <c r="C421" s="7" t="s">
         <v>1092</v>
@@ -14261,7 +14355,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B422" s="7" t="s">
         <v>1094</v>
       </c>
@@ -14281,7 +14375,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="423">
+    <row r="423" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B423" s="7" t="s">
         <v>1097</v>
       </c>
@@ -14301,9 +14395,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B424" s="7">
-        <v>807010.0</v>
+        <v>807010</v>
       </c>
       <c r="C424" s="7" t="s">
         <v>1099</v>
@@ -14321,7 +14415,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="425">
+    <row r="425" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B425" s="7" t="s">
         <v>1101</v>
       </c>
@@ -14341,7 +14435,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B426" s="7" t="s">
         <v>1103</v>
       </c>
@@ -14361,7 +14455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="427">
+    <row r="427" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B427" s="7" t="s">
         <v>1106</v>
       </c>
@@ -14381,7 +14475,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B428" s="7" t="s">
         <v>1109</v>
       </c>
@@ -14401,9 +14495,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="429">
+    <row r="429" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B429" s="7">
-        <v>804048.0</v>
+        <v>804048</v>
       </c>
       <c r="C429" s="7" t="s">
         <v>1111</v>
@@ -14421,7 +14515,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="430">
+    <row r="430" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B430" s="7" t="s">
         <v>1113</v>
       </c>
@@ -14441,7 +14535,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="431">
+    <row r="431" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B431" s="7" t="s">
         <v>1116</v>
       </c>
@@ -14461,7 +14555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B432" s="7" t="s">
         <v>1119</v>
       </c>
@@ -14478,7 +14572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="433">
+    <row r="433" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B433" s="7" t="s">
         <v>1122</v>
       </c>
@@ -14498,7 +14592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B434" s="7" t="s">
         <v>1125</v>
       </c>
@@ -14518,12 +14612,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="435">
+    <row r="435" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B435" s="7">
-        <v>880878.0</v>
+        <v>880878</v>
       </c>
       <c r="C435" s="7">
-        <v>2.1454379E7</v>
+        <v>21454379</v>
       </c>
       <c r="D435" s="7" t="s">
         <v>1128</v>
@@ -14532,18 +14626,18 @@
         <v>33</v>
       </c>
       <c r="F435" s="7">
-        <v>2.1454379E7</v>
+        <v>21454379</v>
       </c>
       <c r="G435" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="436">
+    <row r="436" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B436" s="7">
-        <v>880879.0</v>
+        <v>880879</v>
       </c>
       <c r="C436" s="7">
-        <v>2.0935523E7</v>
+        <v>20935523</v>
       </c>
       <c r="D436" s="7" t="s">
         <v>1129</v>
@@ -14552,18 +14646,18 @@
         <v>33</v>
       </c>
       <c r="F436" s="7">
-        <v>2.0935523E7</v>
+        <v>20935523</v>
       </c>
       <c r="G436" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="437">
+    <row r="437" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B437" s="7">
-        <v>880881.0</v>
+        <v>880881</v>
       </c>
       <c r="C437" s="7">
-        <v>2.0860873E7</v>
+        <v>20860873</v>
       </c>
       <c r="D437" s="7" t="s">
         <v>1130</v>
@@ -14572,13 +14666,13 @@
         <v>33</v>
       </c>
       <c r="F437" s="7">
-        <v>2.0860873E7</v>
+        <v>20860873</v>
       </c>
       <c r="G437" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B438" s="7" t="s">
         <v>1131</v>
       </c>
@@ -14598,7 +14692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B439" s="7" t="s">
         <v>1134</v>
       </c>
@@ -14618,7 +14712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B440" s="7" t="s">
         <v>1137</v>
       </c>
@@ -14638,7 +14732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B441" s="7" t="s">
         <v>1140</v>
       </c>
@@ -14658,7 +14752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="442">
+    <row r="442" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B442" s="7" t="s">
         <v>1143</v>
       </c>
@@ -14678,12 +14772,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="443">
+    <row r="443" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B443" s="7">
-        <v>880883.0</v>
+        <v>880883</v>
       </c>
       <c r="C443" s="7">
-        <v>2.0582558E7</v>
+        <v>20582558</v>
       </c>
       <c r="D443" s="7" t="s">
         <v>1146</v>
@@ -14692,13 +14786,13 @@
         <v>33</v>
       </c>
       <c r="F443" s="7">
-        <v>2.0582558E7</v>
+        <v>20582558</v>
       </c>
       <c r="G443" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="444">
+    <row r="444" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B444" s="7" t="s">
         <v>1147</v>
       </c>
@@ -14718,7 +14812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="445">
+    <row r="445" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B445" s="7" t="s">
         <v>1150</v>
       </c>
@@ -14738,7 +14832,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B446" s="7" t="s">
         <v>1153</v>
       </c>
@@ -14758,7 +14852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="447">
+    <row r="447" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B447" s="7" t="s">
         <v>1156</v>
       </c>
@@ -14778,7 +14872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="448">
+    <row r="448" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B448" s="7" t="s">
         <v>1159</v>
       </c>
@@ -14798,7 +14892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="449">
+    <row r="449" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B449" s="7" t="s">
         <v>1162</v>
       </c>
@@ -14818,7 +14912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B450" s="7" t="s">
         <v>1165</v>
       </c>
@@ -14838,7 +14932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B451" s="7" t="s">
         <v>1168</v>
       </c>
@@ -14858,12 +14952,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B452" s="7">
-        <v>801160.0</v>
+        <v>801160</v>
       </c>
       <c r="C452" s="7">
-        <v>2.1412639E7</v>
+        <v>21412639</v>
       </c>
       <c r="D452" s="7" t="s">
         <v>1171</v>
@@ -14872,13 +14966,13 @@
         <v>33</v>
       </c>
       <c r="F452" s="7">
-        <v>2.1412639E7</v>
+        <v>21412639</v>
       </c>
       <c r="G452" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B453" s="7" t="s">
         <v>1172</v>
       </c>
@@ -14898,7 +14992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B454" s="7" t="s">
         <v>1175</v>
       </c>
@@ -14918,7 +15012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="455">
+    <row r="455" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B455" s="7" t="s">
         <v>1178</v>
       </c>
@@ -14938,7 +15032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B456" s="7" t="s">
         <v>1181</v>
       </c>
@@ -14955,7 +15049,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="457">
+    <row r="457" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B457" s="7" t="s">
         <v>1184</v>
       </c>
@@ -14975,7 +15069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="458">
+    <row r="458" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B458" s="7" t="s">
         <v>1187</v>
       </c>
@@ -14995,7 +15089,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="459">
+    <row r="459" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B459" s="7" t="s">
         <v>1190</v>
       </c>
@@ -15015,7 +15109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="460">
+    <row r="460" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B460" s="7" t="s">
         <v>1193</v>
       </c>
@@ -15035,7 +15129,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B461" s="7" t="s">
         <v>1196</v>
       </c>
@@ -15055,7 +15149,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B462" s="7" t="s">
         <v>1199</v>
       </c>
@@ -15075,7 +15169,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B463" s="7" t="s">
         <v>1202</v>
       </c>
@@ -15095,7 +15189,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="464">
+    <row r="464" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B464" s="7" t="s">
         <v>1205</v>
       </c>
@@ -15115,7 +15209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="465">
+    <row r="465" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B465" s="7" t="s">
         <v>1208</v>
       </c>
@@ -15135,7 +15229,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="466">
+    <row r="466" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B466" s="7" t="s">
         <v>1211</v>
       </c>
@@ -15155,7 +15249,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="467">
+    <row r="467" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B467" s="7" t="s">
         <v>1214</v>
       </c>
@@ -15175,7 +15269,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B468" s="7" t="s">
         <v>1217</v>
       </c>
@@ -15195,7 +15289,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="469">
+    <row r="469" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B469" s="7" t="s">
         <v>1220</v>
       </c>
@@ -15215,7 +15309,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B470" s="7" t="s">
         <v>1222</v>
       </c>
@@ -15235,7 +15329,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B471" s="7" t="s">
         <v>1225</v>
       </c>
@@ -15255,7 +15349,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="472">
+    <row r="472" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B472" s="7" t="s">
         <v>1228</v>
       </c>
@@ -15275,9 +15369,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="473">
+    <row r="473" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B473" s="7">
-        <v>802601.0</v>
+        <v>802601</v>
       </c>
       <c r="C473" s="7" t="s">
         <v>1231</v>
@@ -15295,7 +15389,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B474" s="7" t="s">
         <v>1233</v>
       </c>
@@ -15315,7 +15409,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="475">
+    <row r="475" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B475" s="7" t="s">
         <v>1236</v>
       </c>
@@ -15335,7 +15429,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B476" s="7" t="s">
         <v>1239</v>
       </c>
@@ -15355,7 +15449,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="477">
+    <row r="477" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B477" s="7" t="s">
         <v>1242</v>
       </c>
@@ -15375,7 +15469,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B478" s="7" t="s">
         <v>1245</v>
       </c>
@@ -15395,7 +15489,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="479">
+    <row r="479" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B479" s="7" t="s">
         <v>1248</v>
       </c>
@@ -15415,7 +15509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="480">
+    <row r="480" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B480" s="7" t="s">
         <v>1251</v>
       </c>
@@ -15435,7 +15529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="481">
+    <row r="481" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B481" s="7" t="s">
         <v>1254</v>
       </c>
@@ -15455,7 +15549,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B482" s="7" t="s">
         <v>1257</v>
       </c>
@@ -15475,7 +15569,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="483">
+    <row r="483" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B483" s="7" t="s">
         <v>1260</v>
       </c>
@@ -15495,9 +15589,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B484" s="7">
-        <v>802631.0</v>
+        <v>802631</v>
       </c>
       <c r="C484" s="7" t="s">
         <v>1263</v>
@@ -15515,7 +15609,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="485">
+    <row r="485" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B485" s="7" t="s">
         <v>1265</v>
       </c>
@@ -15535,7 +15629,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="486">
+    <row r="486" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B486" s="7" t="s">
         <v>1268</v>
       </c>
@@ -15555,7 +15649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="487">
+    <row r="487" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B487" s="7" t="s">
         <v>1271</v>
       </c>
@@ -15575,7 +15669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="488">
+    <row r="488" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B488" s="7" t="s">
         <v>1274</v>
       </c>
@@ -15595,9 +15689,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B489" s="7">
-        <v>803737.0</v>
+        <v>803737</v>
       </c>
       <c r="C489" s="7" t="s">
         <v>1277</v>
@@ -15615,12 +15709,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B490" s="7">
-        <v>853714.0</v>
+        <v>853714</v>
       </c>
       <c r="C490" s="7">
-        <v>2.1521353E7</v>
+        <v>21521353</v>
       </c>
       <c r="D490" s="7" t="s">
         <v>1279</v>
@@ -15629,13 +15723,13 @@
         <v>109</v>
       </c>
       <c r="F490" s="7">
-        <v>2.1521353E7</v>
+        <v>21521353</v>
       </c>
       <c r="G490" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="491">
+    <row r="491" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B491" s="7" t="s">
         <v>1280</v>
       </c>
@@ -15655,7 +15749,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="492">
+    <row r="492" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B492" s="7" t="s">
         <v>1283</v>
       </c>
@@ -15675,7 +15769,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="493">
+    <row r="493" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B493" s="7" t="s">
         <v>1285</v>
       </c>
@@ -15695,7 +15789,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B494" s="7" t="s">
         <v>1288</v>
       </c>
@@ -15715,9 +15809,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="495">
+    <row r="495" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C495" s="7">
-        <v>2.0748842E7</v>
+        <v>20748842</v>
       </c>
       <c r="D495" s="7" t="s">
         <v>1291</v>
@@ -15726,15 +15820,15 @@
         <v>10</v>
       </c>
       <c r="F495" s="7">
-        <v>2.0748842E7</v>
+        <v>20748842</v>
       </c>
       <c r="G495" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="496">
+    <row r="496" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C496" s="7">
-        <v>2.0891469E7</v>
+        <v>20891469</v>
       </c>
       <c r="D496" s="7" t="s">
         <v>1291</v>
@@ -15743,15 +15837,15 @@
         <v>10</v>
       </c>
       <c r="F496" s="7">
-        <v>2.0891469E7</v>
+        <v>20891469</v>
       </c>
       <c r="G496" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="497">
+    <row r="497" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C497" s="7">
-        <v>2.0850724E7</v>
+        <v>20850724</v>
       </c>
       <c r="D497" s="7" t="s">
         <v>1291</v>
@@ -15760,13 +15854,13 @@
         <v>10</v>
       </c>
       <c r="F497" s="7">
-        <v>2.0850724E7</v>
+        <v>20850724</v>
       </c>
       <c r="G497" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="498">
+    <row r="498" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C498" s="7" t="s">
         <v>1292</v>
       </c>
@@ -15783,7 +15877,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="499">
+    <row r="499" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C499" s="7" t="s">
         <v>1294</v>
       </c>
@@ -15800,7 +15894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C500" s="7" t="s">
         <v>1296</v>
       </c>
@@ -15817,12 +15911,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B501" s="7" t="s">
         <v>1298</v>
       </c>
       <c r="C501" s="7">
-        <v>2.1016169E7</v>
+        <v>21016169</v>
       </c>
       <c r="D501" s="7" t="s">
         <v>1299</v>
@@ -15831,18 +15925,18 @@
         <v>10</v>
       </c>
       <c r="F501" s="7">
-        <v>2.1016169E7</v>
+        <v>21016169</v>
       </c>
       <c r="G501" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="502">
+    <row r="502" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B502" s="7">
-        <v>841925.0</v>
+        <v>841925</v>
       </c>
       <c r="C502" s="7">
-        <v>2.0824906E7</v>
+        <v>20824906</v>
       </c>
       <c r="D502" s="7" t="s">
         <v>1300</v>
@@ -15851,18 +15945,18 @@
         <v>33</v>
       </c>
       <c r="F502" s="7">
-        <v>2.0824906E7</v>
+        <v>20824906</v>
       </c>
       <c r="G502" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="503">
+    <row r="503" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B503" s="7">
-        <v>842060.0</v>
+        <v>842060</v>
       </c>
       <c r="C503" s="7">
-        <v>2.0864662E7</v>
+        <v>20864662</v>
       </c>
       <c r="D503" s="7" t="s">
         <v>1301</v>
@@ -15871,18 +15965,18 @@
         <v>33</v>
       </c>
       <c r="F503" s="7">
-        <v>2.0864662E7</v>
+        <v>20864662</v>
       </c>
       <c r="G503" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="504">
+    <row r="504" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B504" s="7">
-        <v>2.0513037E7</v>
+        <v>20513037</v>
       </c>
       <c r="C504" s="7">
-        <v>2.1313537E7</v>
+        <v>21313537</v>
       </c>
       <c r="D504" s="7" t="s">
         <v>1302</v>
@@ -15891,15 +15985,15 @@
         <v>33</v>
       </c>
       <c r="F504" s="7">
-        <v>2.1313537E7</v>
+        <v>21313537</v>
       </c>
       <c r="G504" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="505">
+    <row r="505" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B505" s="7">
-        <v>831033.0</v>
+        <v>831033</v>
       </c>
       <c r="C505" s="7" t="s">
         <v>1303</v>
@@ -15917,12 +16011,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="506">
+    <row r="506" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B506" s="7">
-        <v>842071.0</v>
+        <v>842071</v>
       </c>
       <c r="C506" s="7">
-        <v>2.09054E7</v>
+        <v>20905400</v>
       </c>
       <c r="D506" s="7" t="s">
         <v>1305</v>
@@ -15931,13 +16025,13 @@
         <v>33</v>
       </c>
       <c r="F506" s="7">
-        <v>2.09054E7</v>
+        <v>20905400</v>
       </c>
       <c r="G506" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="507">
+    <row r="507" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B507" s="7" t="s">
         <v>1306</v>
       </c>
@@ -15957,7 +16051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="508">
+    <row r="508" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C508" s="7" t="s">
         <v>1309</v>
       </c>
@@ -15974,7 +16068,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="509">
+    <row r="509" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B509" s="7" t="s">
         <v>1311</v>
       </c>
@@ -15994,12 +16088,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="510">
+    <row r="510" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B510" s="7">
-        <v>853717.0</v>
+        <v>853717</v>
       </c>
       <c r="C510" s="7">
-        <v>2.0900982E7</v>
+        <v>20900982</v>
       </c>
       <c r="D510" s="7" t="s">
         <v>1314</v>
@@ -16008,13 +16102,13 @@
         <v>109</v>
       </c>
       <c r="F510" s="7">
-        <v>2.0900982E7</v>
+        <v>20900982</v>
       </c>
       <c r="G510" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="511">
+    <row r="511" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B511" s="7" t="s">
         <v>1315</v>
       </c>
@@ -16034,7 +16128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="512">
+    <row r="512" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B512" s="7" t="s">
         <v>1318</v>
       </c>
@@ -16054,7 +16148,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B513" s="7" t="s">
         <v>1321</v>
       </c>
@@ -16074,7 +16168,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="514">
+    <row r="514" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B514" s="7" t="s">
         <v>1324</v>
       </c>
@@ -16094,7 +16188,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="515">
+    <row r="515" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B515" s="7" t="s">
         <v>1327</v>
       </c>
@@ -16114,7 +16208,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="516">
+    <row r="516" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B516" s="7" t="s">
         <v>1330</v>
       </c>
@@ -16134,7 +16228,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="517">
+    <row r="517" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B517" s="7" t="s">
         <v>1333</v>
       </c>
@@ -16154,7 +16248,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="518">
+    <row r="518" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B518" s="7" t="s">
         <v>1336</v>
       </c>
@@ -16174,7 +16268,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="519">
+    <row r="519" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B519" s="7" t="s">
         <v>1339</v>
       </c>
@@ -16191,9 +16285,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="520">
+    <row r="520" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B520" s="7">
-        <v>853720.0</v>
+        <v>853720</v>
       </c>
       <c r="C520" s="7" t="s">
         <v>1342</v>
@@ -16211,7 +16305,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="521">
+    <row r="521" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B521" s="7" t="s">
         <v>1344</v>
       </c>
@@ -16231,7 +16325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="522">
+    <row r="522" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B522" s="7" t="s">
         <v>1347</v>
       </c>
@@ -16251,7 +16345,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="523">
+    <row r="523" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B523" s="7" t="s">
         <v>1350</v>
       </c>
@@ -16271,7 +16365,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="524">
+    <row r="524" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B524" s="7" t="s">
         <v>1353</v>
       </c>
@@ -16291,7 +16385,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="525">
+    <row r="525" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B525" s="7" t="s">
         <v>1356</v>
       </c>
@@ -16311,12 +16405,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="526">
+    <row r="526" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B526" s="7">
-        <v>891923.0</v>
+        <v>891923</v>
       </c>
       <c r="C526" s="7">
-        <v>2.074261E7</v>
+        <v>20742610</v>
       </c>
       <c r="D526" s="7" t="s">
         <v>1359</v>
@@ -16325,15 +16419,15 @@
         <v>33</v>
       </c>
       <c r="F526" s="7">
-        <v>2.074261E7</v>
+        <v>20742610</v>
       </c>
       <c r="G526" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="527">
+    <row r="527" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B527" s="7">
-        <v>840095.0</v>
+        <v>840095</v>
       </c>
       <c r="C527" s="7" t="s">
         <v>1360</v>
@@ -16348,9 +16442,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="528">
+    <row r="528" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B528" s="7">
-        <v>804047.0</v>
+        <v>804047</v>
       </c>
       <c r="C528" s="7" t="s">
         <v>1362</v>
@@ -16368,7 +16462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="529">
+    <row r="529" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B529" s="7" t="s">
         <v>1364</v>
       </c>
@@ -16388,7 +16482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="530">
+    <row r="530" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B530" s="7" t="s">
         <v>1367</v>
       </c>
@@ -16408,9 +16502,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="531">
+    <row r="531" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B531" s="7">
-        <v>960084.0</v>
+        <v>960084</v>
       </c>
       <c r="C531" s="7" t="s">
         <v>1370</v>
@@ -16428,7 +16522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="532">
+    <row r="532" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B532" s="7" t="s">
         <v>1372</v>
       </c>
@@ -16448,7 +16542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="533">
+    <row r="533" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B533" s="7" t="s">
         <v>1375</v>
       </c>
@@ -16465,7 +16559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="534">
+    <row r="534" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B534" s="7" t="s">
         <v>1378</v>
       </c>
@@ -16485,9 +16579,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="535">
+    <row r="535" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B535" s="7">
-        <v>802538.0</v>
+        <v>802538</v>
       </c>
       <c r="C535" s="7" t="s">
         <v>1381</v>
@@ -16505,7 +16599,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="536">
+    <row r="536" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B536" s="7" t="s">
         <v>1383</v>
       </c>
@@ -16525,7 +16619,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="537">
+    <row r="537" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B537" s="7" t="s">
         <v>1386</v>
       </c>
@@ -16545,7 +16639,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="538">
+    <row r="538" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B538" s="7" t="s">
         <v>1389</v>
       </c>
@@ -16565,7 +16659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="539">
+    <row r="539" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B539" s="7" t="s">
         <v>1392</v>
       </c>
@@ -16585,7 +16679,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="540">
+    <row r="540" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B540" s="7" t="s">
         <v>1395</v>
       </c>
@@ -16605,7 +16699,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="541">
+    <row r="541" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B541" s="7" t="s">
         <v>1398</v>
       </c>
@@ -16625,7 +16719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="542">
+    <row r="542" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B542" s="7" t="s">
         <v>1401</v>
       </c>
@@ -16645,12 +16739,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="543">
+    <row r="543" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B543" s="7">
-        <v>804205.0</v>
+        <v>804205</v>
       </c>
       <c r="C543" s="7">
-        <v>2.5174967E7</v>
+        <v>25174967</v>
       </c>
       <c r="D543" s="7" t="s">
         <v>1404</v>
@@ -16659,13 +16753,13 @@
         <v>67</v>
       </c>
       <c r="F543" s="7">
-        <v>2.5174967E7</v>
+        <v>25174967</v>
       </c>
       <c r="G543" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="544">
+    <row r="544" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B544" s="7" t="s">
         <v>1405</v>
       </c>
@@ -16685,7 +16779,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="545">
+    <row r="545" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B545" s="7" t="s">
         <v>1408</v>
       </c>
@@ -16705,7 +16799,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="546">
+    <row r="546" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B546" s="7" t="s">
         <v>1411</v>
       </c>
@@ -16725,7 +16819,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="547">
+    <row r="547" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B547" s="7" t="s">
         <v>1414</v>
       </c>
@@ -16745,9 +16839,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="548">
+    <row r="548" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B548" s="7">
-        <v>853710.0</v>
+        <v>853710</v>
       </c>
       <c r="C548" s="7" t="s">
         <v>1417</v>
@@ -16765,7 +16859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="549">
+    <row r="549" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B549" s="7" t="s">
         <v>1419</v>
       </c>
@@ -16785,7 +16879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="550">
+    <row r="550" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B550" s="7" t="s">
         <v>1422</v>
       </c>
@@ -16805,7 +16899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="551">
+    <row r="551" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B551" s="7" t="s">
         <v>1425</v>
       </c>
@@ -16825,12 +16919,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="552">
+    <row r="552" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B552" s="7" t="s">
         <v>1427</v>
       </c>
       <c r="C552" s="7">
-        <v>2.1314359E7</v>
+        <v>21314359</v>
       </c>
       <c r="D552" s="7" t="s">
         <v>1428</v>
@@ -16839,15 +16933,15 @@
         <v>67</v>
       </c>
       <c r="F552" s="7">
-        <v>2.1314359E7</v>
+        <v>21314359</v>
       </c>
       <c r="G552" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="553">
+    <row r="553" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B553" s="7">
-        <v>804069.0</v>
+        <v>804069</v>
       </c>
       <c r="C553" s="7" t="s">
         <v>1429</v>
@@ -16862,7 +16956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="554">
+    <row r="554" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B554" s="7" t="s">
         <v>1431</v>
       </c>
@@ -16882,9 +16976,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="555">
+    <row r="555" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B555" s="7">
-        <v>840109.0</v>
+        <v>840109</v>
       </c>
       <c r="C555" s="7" t="s">
         <v>1434</v>
@@ -16902,7 +16996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="556">
+    <row r="556" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B556" s="7" t="s">
         <v>1436</v>
       </c>
@@ -16922,7 +17016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="557">
+    <row r="557" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B557" s="7" t="s">
         <v>1439</v>
       </c>
@@ -16942,12 +17036,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="558">
+    <row r="558" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B558" s="7" t="s">
         <v>1442</v>
       </c>
       <c r="C558" s="7">
-        <v>2.0898038E7</v>
+        <v>20898038</v>
       </c>
       <c r="D558" s="7" t="s">
         <v>1443</v>
@@ -16956,13 +17050,13 @@
         <v>109</v>
       </c>
       <c r="F558" s="7">
-        <v>2.0898038E7</v>
+        <v>20898038</v>
       </c>
       <c r="G558" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="559">
+    <row r="559" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B559" s="7" t="s">
         <v>1444</v>
       </c>
@@ -16982,7 +17076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="560">
+    <row r="560" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C560" s="7" t="s">
         <v>1447</v>
       </c>
@@ -16999,7 +17093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="561">
+    <row r="561" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B561" s="7" t="s">
         <v>1449</v>
       </c>
@@ -17019,7 +17113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="562">
+    <row r="562" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B562" s="7" t="s">
         <v>1452</v>
       </c>
@@ -17039,9 +17133,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="563">
+    <row r="563" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B563" s="7">
-        <v>804134.0</v>
+        <v>804134</v>
       </c>
       <c r="C563" s="7" t="s">
         <v>1455</v>
@@ -17059,12 +17153,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="564">
+    <row r="564" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B564" s="7" t="s">
         <v>1457</v>
       </c>
       <c r="C564" s="7">
-        <v>2.0555313E7</v>
+        <v>20555313</v>
       </c>
       <c r="D564" s="7" t="s">
         <v>1458</v>
@@ -17073,18 +17167,18 @@
         <v>33</v>
       </c>
       <c r="F564" s="7">
-        <v>2.0555313E7</v>
+        <v>20555313</v>
       </c>
       <c r="G564" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="565">
+    <row r="565" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B565" s="7">
-        <v>880830.0</v>
+        <v>880830</v>
       </c>
       <c r="C565" s="7">
-        <v>2.0997341E7</v>
+        <v>20997341</v>
       </c>
       <c r="D565" s="7" t="s">
         <v>1459</v>
@@ -17093,18 +17187,18 @@
         <v>33</v>
       </c>
       <c r="F565" s="7">
-        <v>2.0997341E7</v>
+        <v>20997341</v>
       </c>
       <c r="G565" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="566">
+    <row r="566" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B566" s="7">
-        <v>808157.0</v>
+        <v>808157</v>
       </c>
       <c r="C566" s="7">
-        <v>2.1130919E7</v>
+        <v>21130919</v>
       </c>
       <c r="D566" s="7" t="s">
         <v>1460</v>
@@ -17113,15 +17207,15 @@
         <v>10</v>
       </c>
       <c r="F566" s="7">
-        <v>2.1130919E7</v>
+        <v>21130919</v>
       </c>
       <c r="G566" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="567">
+    <row r="567" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B567" s="7">
-        <v>808153.0</v>
+        <v>808153</v>
       </c>
       <c r="C567" s="7" t="s">
         <v>1461</v>
@@ -17139,7 +17233,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="568">
+    <row r="568" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B568" s="7" t="s">
         <v>1463</v>
       </c>
@@ -17159,7 +17253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="569">
+    <row r="569" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B569" s="7" t="s">
         <v>1466</v>
       </c>
@@ -17179,7 +17273,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="570">
+    <row r="570" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B570" s="7" t="s">
         <v>1469</v>
       </c>
@@ -17199,7 +17293,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="571">
+    <row r="571" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B571" s="7" t="s">
         <v>1472</v>
       </c>
@@ -17219,7 +17313,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="572">
+    <row r="572" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B572" s="7" t="s">
         <v>1475</v>
       </c>
@@ -17239,7 +17333,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="573">
+    <row r="573" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B573" s="7" t="s">
         <v>1478</v>
       </c>
@@ -17259,7 +17353,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="574">
+    <row r="574" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C574" s="7" t="s">
         <v>1481</v>
       </c>
@@ -17273,7 +17367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="575">
+    <row r="575" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C575" s="7" t="s">
         <v>1482</v>
       </c>
@@ -17287,7 +17381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="576">
+    <row r="576" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B576" s="7" t="s">
         <v>1483</v>
       </c>
@@ -17304,7 +17398,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="577">
+    <row r="577" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C577" s="7" t="s">
         <v>1485</v>
       </c>
@@ -17321,12 +17415,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="578">
+    <row r="578" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B578" s="7">
-        <v>845069.0</v>
+        <v>845069</v>
       </c>
       <c r="C578" s="7">
-        <v>2.0513343E7</v>
+        <v>20513343</v>
       </c>
       <c r="D578" s="7" t="s">
         <v>1487</v>
@@ -17335,13 +17429,13 @@
         <v>109</v>
       </c>
       <c r="F578" s="7">
-        <v>2.0513343E7</v>
+        <v>20513343</v>
       </c>
       <c r="G578" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="579">
+    <row r="579" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B579" s="7" t="s">
         <v>1488</v>
       </c>
@@ -17361,7 +17455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="580">
+    <row r="580" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B580" s="7" t="s">
         <v>1491</v>
       </c>
@@ -17378,7 +17472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="581">
+    <row r="581" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B581" s="7" t="s">
         <v>1494</v>
       </c>
@@ -17398,7 +17492,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="582">
+    <row r="582" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B582" s="7" t="s">
         <v>1497</v>
       </c>
@@ -17418,12 +17512,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="583">
+    <row r="583" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B583" s="7">
-        <v>801170.0</v>
+        <v>801170</v>
       </c>
       <c r="C583" s="7">
-        <v>2.1905526E7</v>
+        <v>21905526</v>
       </c>
       <c r="D583" s="7" t="s">
         <v>1500</v>
@@ -17432,13 +17526,13 @@
         <v>33</v>
       </c>
       <c r="F583" s="7">
-        <v>2.1905526E7</v>
+        <v>21905526</v>
       </c>
       <c r="G583" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="584">
+    <row r="584" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B584" s="7" t="s">
         <v>1501</v>
       </c>
@@ -17458,7 +17552,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="585">
+    <row r="585" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B585" s="7" t="s">
         <v>1504</v>
       </c>
@@ -17478,7 +17572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="586">
+    <row r="586" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B586" s="7" t="s">
         <v>1507</v>
       </c>
@@ -17498,9 +17592,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="587">
+    <row r="587" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B587" s="7">
-        <v>803885.0</v>
+        <v>803885</v>
       </c>
       <c r="C587" s="7" t="s">
         <v>1510</v>
@@ -17518,9 +17612,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="588">
+    <row r="588" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B588" s="7">
-        <v>960152.0</v>
+        <v>960152</v>
       </c>
       <c r="C588" s="7" t="s">
         <v>1512</v>
@@ -17535,12 +17629,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="589">
+    <row r="589" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B589" s="7">
-        <v>880832.0</v>
+        <v>880832</v>
       </c>
       <c r="C589" s="7">
-        <v>2.1307197E7</v>
+        <v>21307197</v>
       </c>
       <c r="D589" s="7" t="s">
         <v>1514</v>
@@ -17549,13 +17643,13 @@
         <v>33</v>
       </c>
       <c r="F589" s="7">
-        <v>2.1307197E7</v>
+        <v>21307197</v>
       </c>
       <c r="G589" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="590">
+    <row r="590" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B590" s="7" t="s">
         <v>1515</v>
       </c>
@@ -17575,7 +17669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="591">
+    <row r="591" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B591" s="7" t="s">
         <v>1518</v>
       </c>
@@ -17595,7 +17689,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="592">
+    <row r="592" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C592" s="7" t="s">
         <v>1521</v>
       </c>
@@ -17612,7 +17706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="593">
+    <row r="593" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C593" s="7" t="s">
         <v>1523</v>
       </c>
@@ -17629,7 +17723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="594">
+    <row r="594" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C594" s="7" t="s">
         <v>1525</v>
       </c>
@@ -17643,7 +17737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="595">
+    <row r="595" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C595" s="7" t="s">
         <v>1527</v>
       </c>
@@ -17657,7 +17751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="596">
+    <row r="596" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C596" s="12" t="s">
         <v>1529</v>
       </c>
@@ -17671,7 +17765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="597">
+    <row r="597" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C597" s="7" t="s">
         <v>1531</v>
       </c>
@@ -17685,7 +17779,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="598">
+    <row r="598" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B598" s="7" t="s">
         <v>1533</v>
       </c>
@@ -17702,9 +17796,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="599">
+    <row r="599" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B599" s="7">
-        <v>803736.0</v>
+        <v>803736</v>
       </c>
       <c r="C599" s="7" t="s">
         <v>1535</v>
@@ -17719,7 +17813,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="600">
+    <row r="600" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B600" s="7" t="s">
         <v>1537</v>
       </c>
@@ -17736,12 +17830,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="601">
+    <row r="601" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B601" s="7">
-        <v>880865.0</v>
+        <v>880865</v>
       </c>
       <c r="C601" s="7">
-        <v>2.0582557E7</v>
+        <v>20582557</v>
       </c>
       <c r="D601" s="7" t="s">
         <v>1540</v>
@@ -17750,13 +17844,13 @@
         <v>33</v>
       </c>
       <c r="F601" s="7">
-        <v>2.0582557E7</v>
+        <v>20582557</v>
       </c>
       <c r="G601" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="602">
+    <row r="602" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B602" s="7" t="s">
         <v>1541</v>
       </c>
@@ -17776,7 +17870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="603">
+    <row r="603" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B603" s="7" t="s">
         <v>1544</v>
       </c>
@@ -17796,7 +17890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="604">
+    <row r="604" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B604" s="7" t="s">
         <v>1547</v>
       </c>
@@ -17816,7 +17910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="605">
+    <row r="605" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B605" s="7" t="s">
         <v>1550</v>
       </c>
@@ -17836,7 +17930,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="606">
+    <row r="606" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B606" s="7" t="s">
         <v>1553</v>
       </c>
@@ -17853,7 +17947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="607">
+    <row r="607" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B607" s="7" t="s">
         <v>1556</v>
       </c>
@@ -17870,7 +17964,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="608">
+    <row r="608" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B608" s="7" t="s">
         <v>1559</v>
       </c>
@@ -17887,26 +17981,26 @@
         <v>11</v>
       </c>
     </row>
-    <row r="609">
+    <row r="609" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B609" s="7">
-        <v>841950.0</v>
+        <v>841950</v>
       </c>
       <c r="C609" s="7">
-        <v>2.0505537E7</v>
+        <v>20505537</v>
       </c>
       <c r="D609" s="7" t="s">
         <v>1562</v>
       </c>
       <c r="F609" s="7">
-        <v>2.0505537E7</v>
+        <v>20505537</v>
       </c>
       <c r="G609" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="610">
+    <row r="610" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B610" s="7">
-        <v>740226.0</v>
+        <v>740226</v>
       </c>
       <c r="C610" s="7" t="s">
         <v>1563</v>
@@ -17924,7 +18018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="611">
+    <row r="611" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B611" s="7" t="s">
         <v>1565</v>
       </c>
@@ -17944,7 +18038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="612">
+    <row r="612" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B612" s="7" t="s">
         <v>1568</v>
       </c>
@@ -17964,7 +18058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="613">
+    <row r="613" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B613" s="7" t="s">
         <v>1571</v>
       </c>
@@ -17984,7 +18078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="614">
+    <row r="614" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B614" s="7" t="s">
         <v>1574</v>
       </c>
@@ -18004,7 +18098,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="615">
+    <row r="615" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B615" s="7" t="s">
         <v>1577</v>
       </c>
@@ -18024,7 +18118,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="616">
+    <row r="616" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B616" s="7" t="s">
         <v>1580</v>
       </c>
@@ -18044,7 +18138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="617">
+    <row r="617" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B617" s="7" t="s">
         <v>1583</v>
       </c>
@@ -18061,7 +18155,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="618">
+    <row r="618" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B618" s="7" t="s">
         <v>1586</v>
       </c>
@@ -18078,7 +18172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="619">
+    <row r="619" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B619" s="7" t="s">
         <v>1588</v>
       </c>
@@ -18095,7 +18189,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="620">
+    <row r="620" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B620" s="7" t="s">
         <v>1591</v>
       </c>
@@ -18112,7 +18206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="621">
+    <row r="621" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B621" s="7" t="s">
         <v>1594</v>
       </c>
@@ -18129,7 +18223,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="622">
+    <row r="622" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B622" s="7" t="s">
         <v>1597</v>
       </c>
@@ -18149,7 +18243,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="623">
+    <row r="623" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B623" s="7" t="s">
         <v>1599</v>
       </c>
@@ -18169,7 +18263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="624">
+    <row r="624" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B624" s="7" t="s">
         <v>1602</v>
       </c>
@@ -18189,7 +18283,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="625">
+    <row r="625" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B625" s="7" t="s">
         <v>1605</v>
       </c>
@@ -18209,7 +18303,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="626">
+    <row r="626" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B626" s="7" t="s">
         <v>1608</v>
       </c>
@@ -18229,7 +18323,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="627">
+    <row r="627" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B627" s="7" t="s">
         <v>1611</v>
       </c>
@@ -18249,7 +18343,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="628">
+    <row r="628" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B628" s="7" t="s">
         <v>1614</v>
       </c>
@@ -18269,7 +18363,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="629">
+    <row r="629" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B629" s="7" t="s">
         <v>1617</v>
       </c>
@@ -18289,7 +18383,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="630">
+    <row r="630" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B630" s="7" t="s">
         <v>1620</v>
       </c>
@@ -18309,7 +18403,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="631">
+    <row r="631" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B631" s="7" t="s">
         <v>1556</v>
       </c>
@@ -18329,7 +18423,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="632">
+    <row r="632" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B632" s="7" t="s">
         <v>1625</v>
       </c>
@@ -18349,12 +18443,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="633">
+    <row r="633" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B633" s="7">
-        <v>831032.0</v>
+        <v>831032</v>
       </c>
       <c r="C633" s="7">
-        <v>2.080585E7</v>
+        <v>20805850</v>
       </c>
       <c r="D633" s="7" t="s">
         <v>1628</v>
@@ -18363,27 +18457,27 @@
         <v>33</v>
       </c>
       <c r="F633" s="7">
-        <v>2.080585E7</v>
+        <v>20805850</v>
       </c>
       <c r="G633" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="634">
+    <row r="634" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C634" s="7">
-        <v>607.0</v>
+        <v>607</v>
       </c>
       <c r="D634" s="7" t="s">
         <v>1629</v>
       </c>
       <c r="F634" s="7">
-        <v>607.0</v>
+        <v>607</v>
       </c>
       <c r="G634" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="635">
+    <row r="635" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B635" s="7" t="s">
         <v>1630</v>
       </c>
@@ -18403,7 +18497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="636">
+    <row r="636" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B636" s="7" t="s">
         <v>1633</v>
       </c>
@@ -18423,7 +18517,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="637">
+    <row r="637" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B637" s="7" t="s">
         <v>1636</v>
       </c>
@@ -18443,7 +18537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="638">
+    <row r="638" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B638" s="7" t="s">
         <v>1638</v>
       </c>
@@ -18463,12 +18557,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="639">
+    <row r="639" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B639" s="7">
-        <v>831051.0</v>
+        <v>831051</v>
       </c>
       <c r="C639" s="7">
-        <v>2.1293367E7</v>
+        <v>21293367</v>
       </c>
       <c r="D639" s="7" t="s">
         <v>1641</v>
@@ -18477,18 +18571,18 @@
         <v>33</v>
       </c>
       <c r="F639" s="7">
-        <v>2.1293367E7</v>
+        <v>21293367</v>
       </c>
       <c r="G639" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="640">
+    <row r="640" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B640" s="7">
-        <v>821069.0</v>
+        <v>821069</v>
       </c>
       <c r="C640" s="7">
-        <v>1547254.0</v>
+        <v>1547254</v>
       </c>
       <c r="D640" s="7" t="s">
         <v>1642</v>
@@ -18497,18 +18591,18 @@
         <v>33</v>
       </c>
       <c r="F640" s="7">
-        <v>1547254.0</v>
+        <v>1547254</v>
       </c>
       <c r="G640" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="641">
+    <row r="641" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B641" s="7">
-        <v>840046.0</v>
+        <v>840046</v>
       </c>
       <c r="C641" s="7">
-        <v>2.1021925E7</v>
+        <v>21021925</v>
       </c>
       <c r="D641" s="7" t="s">
         <v>1643</v>
@@ -18517,13 +18611,13 @@
         <v>33</v>
       </c>
       <c r="F641" s="7">
-        <v>2.1021925E7</v>
+        <v>21021925</v>
       </c>
       <c r="G641" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="642">
+    <row r="642" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B642" s="7" t="s">
         <v>1644</v>
       </c>
@@ -18543,7 +18637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="643">
+    <row r="643" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B643" s="7" t="s">
         <v>1647</v>
       </c>
@@ -18563,9 +18657,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="644">
+    <row r="644" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B644" s="7">
-        <v>803906.0</v>
+        <v>803906</v>
       </c>
       <c r="C644" s="7" t="s">
         <v>1650</v>
@@ -18583,7 +18677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="645">
+    <row r="645" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B645" s="7" t="s">
         <v>1652</v>
       </c>
@@ -18600,12 +18694,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="646">
+    <row r="646" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B646" s="7">
-        <v>845011.0</v>
+        <v>845011</v>
       </c>
       <c r="C646" s="7">
-        <v>2.0768519E7</v>
+        <v>20768519</v>
       </c>
       <c r="D646" s="7" t="s">
         <v>1655</v>
@@ -18614,18 +18708,18 @@
         <v>33</v>
       </c>
       <c r="F646" s="7">
-        <v>2.0768519E7</v>
+        <v>20768519</v>
       </c>
       <c r="G646" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="647">
+    <row r="647" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B647" s="7">
-        <v>845041.0</v>
+        <v>845041</v>
       </c>
       <c r="C647" s="7">
-        <v>2.0740804E7</v>
+        <v>20740804</v>
       </c>
       <c r="D647" s="7" t="s">
         <v>1656</v>
@@ -18634,18 +18728,18 @@
         <v>33</v>
       </c>
       <c r="F647" s="7">
-        <v>2.0740804E7</v>
+        <v>20740804</v>
       </c>
       <c r="G647" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="648">
+    <row r="648" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B648" s="7">
-        <v>845042.0</v>
+        <v>845042</v>
       </c>
       <c r="C648" s="7">
-        <v>2.0530103E7</v>
+        <v>20530103</v>
       </c>
       <c r="D648" s="7" t="s">
         <v>1657</v>
@@ -18654,18 +18748,18 @@
         <v>33</v>
       </c>
       <c r="F648" s="7">
-        <v>2.0530103E7</v>
+        <v>20530103</v>
       </c>
       <c r="G648" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="649">
+    <row r="649" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B649" s="7">
-        <v>891990.0</v>
+        <v>891990</v>
       </c>
       <c r="C649" s="7">
-        <v>3183368.0</v>
+        <v>3183368</v>
       </c>
       <c r="D649" s="7" t="s">
         <v>1658</v>
@@ -18674,15 +18768,15 @@
         <v>33</v>
       </c>
       <c r="F649" s="7">
-        <v>3183368.0</v>
+        <v>3183368</v>
       </c>
       <c r="G649" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="650">
+    <row r="650" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B650" s="7">
-        <v>808141.0</v>
+        <v>808141</v>
       </c>
       <c r="C650" s="7" t="s">
         <v>1659</v>
@@ -18697,9 +18791,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="651">
+    <row r="651" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B651" s="7">
-        <v>805153.0</v>
+        <v>805153</v>
       </c>
       <c r="C651" s="7" t="s">
         <v>1461</v>
@@ -18714,9 +18808,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="652">
+    <row r="652" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B652" s="7">
-        <v>750220.0</v>
+        <v>750220</v>
       </c>
       <c r="C652" s="7" t="s">
         <v>1662</v>
@@ -18734,7 +18828,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="653">
+    <row r="653" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B653" s="7" t="s">
         <v>1664</v>
       </c>
@@ -18754,12 +18848,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="654">
+    <row r="654" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B654" s="7">
-        <v>845010.0</v>
+        <v>845010</v>
       </c>
       <c r="C654" s="7">
-        <v>2.0740798E7</v>
+        <v>20740798</v>
       </c>
       <c r="D654" s="7" t="s">
         <v>1667</v>
@@ -18768,18 +18862,18 @@
         <v>33</v>
       </c>
       <c r="F654" s="7">
-        <v>2.0740798E7</v>
+        <v>20740798</v>
       </c>
       <c r="G654" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="655">
+    <row r="655" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B655" s="7">
-        <v>842060.0</v>
+        <v>842060</v>
       </c>
       <c r="C655" s="7">
-        <v>2.0864662E7</v>
+        <v>20864662</v>
       </c>
       <c r="D655" s="7" t="s">
         <v>1301</v>
@@ -18788,13 +18882,13 @@
         <v>33</v>
       </c>
       <c r="F655" s="7">
-        <v>2.0864662E7</v>
+        <v>20864662</v>
       </c>
       <c r="G655" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="656">
+    <row r="656" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B656" s="7" t="s">
         <v>1668</v>
       </c>
@@ -18814,21 +18908,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="657">
+    <row r="657" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C657" s="7">
-        <v>2.253985E7</v>
+        <v>22539850</v>
       </c>
       <c r="D657" s="7" t="s">
         <v>1671</v>
       </c>
       <c r="F657" s="7">
-        <v>2.253985E7</v>
+        <v>22539850</v>
       </c>
       <c r="G657" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="658">
+    <row r="658" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B658" s="7" t="s">
         <v>1672</v>
       </c>
@@ -18848,7 +18942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="659">
+    <row r="659" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B659" s="7" t="s">
         <v>1674</v>
       </c>
@@ -18865,7 +18959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="660">
+    <row r="660" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B660" s="7" t="s">
         <v>1675</v>
       </c>
@@ -18882,7 +18976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="661">
+    <row r="661" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B661" s="7" t="s">
         <v>1676</v>
       </c>
@@ -18899,7 +18993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="662">
+    <row r="662" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B662" s="7" t="s">
         <v>1679</v>
       </c>
@@ -18919,9 +19013,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="663">
+    <row r="663" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B663" s="7">
-        <v>806765.0</v>
+        <v>806765</v>
       </c>
       <c r="C663" s="7" t="s">
         <v>1682</v>
@@ -18939,9 +19033,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="664">
+    <row r="664" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B664" s="7">
-        <v>808142.0</v>
+        <v>808142</v>
       </c>
       <c r="C664" s="7" t="s">
         <v>1683</v>
@@ -18959,9 +19053,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="665">
+    <row r="665" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B665" s="7">
-        <v>808149.0</v>
+        <v>808149</v>
       </c>
       <c r="C665" s="7" t="s">
         <v>1685</v>
@@ -18979,9 +19073,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="666">
+    <row r="666" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B666" s="7">
-        <v>808140.0</v>
+        <v>808140</v>
       </c>
       <c r="C666" s="7" t="s">
         <v>1687</v>
@@ -18999,7 +19093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="667">
+    <row r="667" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B667" s="7" t="s">
         <v>1689</v>
       </c>
@@ -19019,7 +19113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="668">
+    <row r="668" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C668" s="7" t="s">
         <v>1692</v>
       </c>
@@ -19033,7 +19127,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="669">
+    <row r="669" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B669" s="7" t="s">
         <v>1694</v>
       </c>
@@ -19053,7 +19147,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="670">
+    <row r="670" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B670" s="7" t="s">
         <v>1697</v>
       </c>
@@ -19073,12 +19167,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="671">
+    <row r="671" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B671" s="7">
-        <v>821013.0</v>
+        <v>821013</v>
       </c>
       <c r="C671" s="7">
-        <v>2.0536487E7</v>
+        <v>20536487</v>
       </c>
       <c r="D671" s="7" t="s">
         <v>1700</v>
@@ -19087,18 +19181,18 @@
         <v>33</v>
       </c>
       <c r="F671" s="7">
-        <v>2.0536487E7</v>
+        <v>20536487</v>
       </c>
       <c r="G671" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="672">
+    <row r="672" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B672" s="7">
-        <v>821022.0</v>
+        <v>821022</v>
       </c>
       <c r="C672" s="7">
-        <v>270950.0</v>
+        <v>270950</v>
       </c>
       <c r="D672" s="7" t="s">
         <v>1701</v>
@@ -19107,18 +19201,18 @@
         <v>33</v>
       </c>
       <c r="F672" s="7">
-        <v>270950.0</v>
+        <v>270950</v>
       </c>
       <c r="G672" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="673">
+    <row r="673" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B673" s="7">
-        <v>853716.0</v>
+        <v>853716</v>
       </c>
       <c r="C673" s="7">
-        <v>2.2564822E7</v>
+        <v>22564822</v>
       </c>
       <c r="D673" s="7" t="s">
         <v>1702</v>
@@ -19127,18 +19221,18 @@
         <v>109</v>
       </c>
       <c r="F673" s="7">
-        <v>2.2564822E7</v>
+        <v>22564822</v>
       </c>
       <c r="G673" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="674">
+    <row r="674" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B674" s="7">
-        <v>831056.0</v>
+        <v>831056</v>
       </c>
       <c r="C674" s="7">
-        <v>2.0479636E7</v>
+        <v>20479636</v>
       </c>
       <c r="D674" s="7" t="s">
         <v>1703</v>
@@ -19147,18 +19241,18 @@
         <v>33</v>
       </c>
       <c r="F674" s="7">
-        <v>2.0479636E7</v>
+        <v>20479636</v>
       </c>
       <c r="G674" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="675">
+    <row r="675" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B675" s="7">
-        <v>840071.0</v>
+        <v>840071</v>
       </c>
       <c r="C675" s="7">
-        <v>2.1458307E7</v>
+        <v>21458307</v>
       </c>
       <c r="D675" s="7" t="s">
         <v>1704</v>
@@ -19167,18 +19261,18 @@
         <v>109</v>
       </c>
       <c r="F675" s="7">
-        <v>2.1458307E7</v>
+        <v>21458307</v>
       </c>
       <c r="G675" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="676">
+    <row r="676" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B676" s="7">
-        <v>836005.0</v>
+        <v>836005</v>
       </c>
       <c r="C676" s="7">
-        <v>2.0852765E7</v>
+        <v>20852765</v>
       </c>
       <c r="D676" s="7" t="s">
         <v>1705</v>
@@ -19187,13 +19281,13 @@
         <v>33</v>
       </c>
       <c r="F676" s="7">
-        <v>2.0852765E7</v>
+        <v>20852765</v>
       </c>
       <c r="G676" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="677">
+    <row r="677" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B677" s="7" t="s">
         <v>1706</v>
       </c>
@@ -19213,7 +19307,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="678">
+    <row r="678" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B678" s="7" t="s">
         <v>1709</v>
       </c>
@@ -19230,63 +19324,63 @@
         <v>11</v>
       </c>
     </row>
-    <row r="679">
+    <row r="679" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C679" s="7">
-        <v>2.0891469E7</v>
+        <v>20891469</v>
       </c>
       <c r="D679" s="7" t="s">
         <v>1712</v>
       </c>
       <c r="F679" s="7">
-        <v>2.0891469E7</v>
+        <v>20891469</v>
       </c>
       <c r="G679" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="680">
+    <row r="680" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C680" s="7">
-        <v>2.2081687E7</v>
+        <v>22081687</v>
       </c>
       <c r="D680" s="7" t="s">
         <v>1291</v>
       </c>
       <c r="F680" s="7">
-        <v>2.2081687E7</v>
+        <v>22081687</v>
       </c>
       <c r="G680" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="681">
+    <row r="681" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C681" s="7">
-        <v>8131848.0</v>
+        <v>8131848</v>
       </c>
       <c r="D681" s="7" t="s">
         <v>1713</v>
       </c>
       <c r="F681" s="7">
-        <v>8131848.0</v>
+        <v>8131848</v>
       </c>
       <c r="G681" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="682">
+    <row r="682" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C682" s="7">
-        <v>2.0743004E7</v>
+        <v>20743004</v>
       </c>
       <c r="D682" s="7" t="s">
         <v>1291</v>
       </c>
       <c r="F682" s="7">
-        <v>2.0743004E7</v>
+        <v>20743004</v>
       </c>
       <c r="G682" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="683">
+    <row r="683" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B683" s="7" t="s">
         <v>1714</v>
       </c>
@@ -19303,29 +19397,29 @@
         <v>11</v>
       </c>
     </row>
-    <row r="684">
+    <row r="684" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B684" s="7">
-        <v>891989.0</v>
+        <v>891989</v>
       </c>
       <c r="C684" s="7">
-        <v>8.5137065E7</v>
+        <v>85137065</v>
       </c>
       <c r="D684" s="7" t="s">
         <v>1717</v>
       </c>
       <c r="F684" s="7">
-        <v>8.5137065E7</v>
+        <v>85137065</v>
       </c>
       <c r="G684" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="685">
+    <row r="685" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B685" s="7">
-        <v>421047.0</v>
+        <v>421047</v>
       </c>
       <c r="C685" s="7">
-        <v>3539944.0</v>
+        <v>3539944</v>
       </c>
       <c r="D685" s="7" t="s">
         <v>1718</v>
@@ -19334,13 +19428,13 @@
         <v>33</v>
       </c>
       <c r="F685" s="7">
-        <v>3539944.0</v>
+        <v>3539944</v>
       </c>
       <c r="G685" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="686">
+    <row r="686" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B686" s="7" t="s">
         <v>1719</v>
       </c>
@@ -19360,7 +19454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="687">
+    <row r="687" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B687" s="7" t="s">
         <v>1722</v>
       </c>
@@ -19377,9 +19471,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="688">
+    <row r="688" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B688" s="7">
-        <v>750731.0</v>
+        <v>750731</v>
       </c>
       <c r="C688" s="7" t="s">
         <v>1725</v>
@@ -19397,7 +19491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="689">
+    <row r="689" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B689" s="7" t="s">
         <v>1727</v>
       </c>
@@ -19414,7 +19508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="690">
+    <row r="690" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B690" s="7" t="s">
         <v>1730</v>
       </c>
@@ -19434,7 +19528,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="691">
+    <row r="691" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B691" s="7" t="s">
         <v>1731</v>
       </c>
@@ -19454,7 +19548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="692">
+    <row r="692" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C692" s="7" t="s">
         <v>1687</v>
       </c>
@@ -19468,7 +19562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="693">
+    <row r="693" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C693" s="7" t="s">
         <v>1735</v>
       </c>
@@ -19482,24 +19576,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="694">
+    <row r="694" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B694" s="7">
-        <v>808157.0</v>
+        <v>808157</v>
       </c>
       <c r="C694" s="7">
-        <v>2.1130919E7</v>
+        <v>21130919</v>
       </c>
       <c r="D694" s="7" t="s">
         <v>1737</v>
       </c>
       <c r="F694" s="7">
-        <v>2.1130919E7</v>
+        <v>21130919</v>
       </c>
       <c r="G694" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="695">
+    <row r="695" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C695" s="7" t="s">
         <v>1683</v>
       </c>
@@ -19513,9 +19607,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="696">
+    <row r="696" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B696" s="7">
-        <v>804126.0</v>
+        <v>804126</v>
       </c>
       <c r="C696" s="7" t="s">
         <v>1739</v>
@@ -19533,12 +19627,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="697">
+    <row r="697" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B697" s="7">
-        <v>831039.0</v>
+        <v>831039</v>
       </c>
       <c r="C697" s="7">
-        <v>2.1294062E7</v>
+        <v>21294062</v>
       </c>
       <c r="D697" s="7" t="s">
         <v>1740</v>
@@ -19547,13 +19641,13 @@
         <v>33</v>
       </c>
       <c r="F697" s="7">
-        <v>2.1294062E7</v>
+        <v>21294062</v>
       </c>
       <c r="G697" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="698">
+    <row r="698" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B698" s="7" t="s">
         <v>1741</v>
       </c>
@@ -19570,7 +19664,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="699">
+    <row r="699" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B699" s="7" t="s">
         <v>1744</v>
       </c>
@@ -19590,7 +19684,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="700">
+    <row r="700" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B700" s="7" t="s">
         <v>1747</v>
       </c>
@@ -19610,7 +19704,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="701">
+    <row r="701" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B701" s="7" t="s">
         <v>1750</v>
       </c>
@@ -19630,7 +19724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="702">
+    <row r="702" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B702" s="7" t="s">
         <v>1753</v>
       </c>
@@ -19650,7 +19744,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="703">
+    <row r="703" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B703" s="7" t="s">
         <v>1756</v>
       </c>
@@ -19670,12 +19764,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="704">
+    <row r="704" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B704" s="7">
-        <v>808158.0</v>
+        <v>808158</v>
       </c>
       <c r="C704" s="7">
-        <v>2.1130954E7</v>
+        <v>21130954</v>
       </c>
       <c r="D704" s="7" t="s">
         <v>1759</v>
@@ -19684,13 +19778,13 @@
         <v>10</v>
       </c>
       <c r="F704" s="7">
-        <v>2.1130954E7</v>
+        <v>21130954</v>
       </c>
       <c r="G704" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="705">
+    <row r="705" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B705" s="7" t="s">
         <v>1760</v>
       </c>
@@ -19710,7 +19804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="706">
+    <row r="706" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B706" s="7" t="s">
         <v>1763</v>
       </c>
@@ -19730,7 +19824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="707">
+    <row r="707" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B707" s="7" t="s">
         <v>1766</v>
       </c>
@@ -19750,9 +19844,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="708">
+    <row r="708" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B708" s="7">
-        <v>840030.0</v>
+        <v>840030</v>
       </c>
       <c r="C708" s="7" t="s">
         <v>1769</v>
@@ -19770,7 +19864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="709">
+    <row r="709" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B709" s="7" t="s">
         <v>1771</v>
       </c>
@@ -19790,7 +19884,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="710">
+    <row r="710" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B710" s="7" t="s">
         <v>1773</v>
       </c>
@@ -19810,7 +19904,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="711">
+    <row r="711" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B711" s="7" t="s">
         <v>1776</v>
       </c>
@@ -19830,9 +19924,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="712">
+    <row r="712" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B712" s="7">
-        <v>802611.0</v>
+        <v>802611</v>
       </c>
       <c r="C712" s="7" t="s">
         <v>1779</v>
@@ -19850,12 +19944,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="713">
+    <row r="713" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B713" s="7">
-        <v>891991.0</v>
+        <v>891991</v>
       </c>
       <c r="C713" s="7">
-        <v>8.5124276E7</v>
+        <v>85124276</v>
       </c>
       <c r="D713" s="7" t="s">
         <v>1781</v>
@@ -19864,15 +19958,15 @@
         <v>33</v>
       </c>
       <c r="F713" s="7">
-        <v>8.5124276E7</v>
+        <v>85124276</v>
       </c>
       <c r="G713" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="714">
+    <row r="714" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="C714" s="7">
-        <v>2.1485016E7</v>
+        <v>21485016</v>
       </c>
       <c r="D714" s="7" t="s">
         <v>1782</v>
@@ -19881,13 +19975,13 @@
         <v>33</v>
       </c>
       <c r="F714" s="7">
-        <v>2.1485016E7</v>
+        <v>21485016</v>
       </c>
       <c r="G714" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="715">
+    <row r="715" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B715" s="7" t="s">
         <v>1783</v>
       </c>
@@ -19907,9 +20001,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="716">
+    <row r="716" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B716" s="7">
-        <v>871070.0</v>
+        <v>871070</v>
       </c>
       <c r="C716" s="7" t="s">
         <v>1786</v>
@@ -19927,7 +20021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="717">
+    <row r="717" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B717" s="7" t="s">
         <v>1788</v>
       </c>
@@ -19947,9 +20041,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="718">
+    <row r="718" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B718" s="7">
-        <v>3421.0</v>
+        <v>3421</v>
       </c>
       <c r="C718" s="7" t="s">
         <v>1791</v>
@@ -19967,7 +20061,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="719">
+    <row r="719" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B719" s="7" t="s">
         <v>1793</v>
       </c>
@@ -19987,9 +20081,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="720">
+    <row r="720" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B720" s="7">
-        <v>808157.0</v>
+        <v>808157</v>
       </c>
       <c r="C720" s="7" t="s">
         <v>1796</v>
@@ -20007,9 +20101,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="721">
+    <row r="721" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B721" s="7">
-        <v>802602.0</v>
+        <v>802602</v>
       </c>
       <c r="C721" s="7" t="s">
         <v>1798</v>
@@ -20024,9 +20118,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="722">
+    <row r="722" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B722" s="7">
-        <v>900135.0</v>
+        <v>900135</v>
       </c>
       <c r="C722" s="7" t="s">
         <v>1800</v>
@@ -20044,7 +20138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="723">
+    <row r="723" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B723" s="7" t="s">
         <v>1803</v>
       </c>
@@ -20064,7 +20158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="724">
+    <row r="724" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B724" s="7" t="s">
         <v>1806</v>
       </c>
@@ -20084,7 +20178,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="725">
+    <row r="725" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B725" s="7" t="s">
         <v>1809</v>
       </c>
@@ -20104,7 +20198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="726">
+    <row r="726" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B726" s="7" t="s">
         <v>1812</v>
       </c>
@@ -20124,7 +20218,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="727">
+    <row r="727" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B727" s="7" t="s">
         <v>1815</v>
       </c>
@@ -20144,7 +20238,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="728">
+    <row r="728" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B728" s="7" t="s">
         <v>1818</v>
       </c>
@@ -20164,7 +20258,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="729">
+    <row r="729" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B729" s="7" t="s">
         <v>1821</v>
       </c>
@@ -20184,7 +20278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="730">
+    <row r="730" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B730" s="7" t="s">
         <v>1823</v>
       </c>
@@ -20204,68 +20298,508 @@
         <v>11</v>
       </c>
     </row>
-    <row r="731">
-      <c r="B731" s="13" t="s">
+    <row r="731" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B731" s="7" t="s">
         <v>1826</v>
       </c>
-      <c r="C731" s="13" t="s">
+      <c r="C731" s="7" t="s">
         <v>1826</v>
       </c>
-      <c r="D731" s="13" t="s">
+      <c r="D731" s="7" t="s">
         <v>1827</v>
       </c>
       <c r="E731" s="7" t="s">
         <v>1828</v>
       </c>
-      <c r="F731" s="13" t="s">
+      <c r="F731" s="7" t="s">
         <v>1826</v>
       </c>
       <c r="G731" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="732">
-      <c r="B732" s="13" t="s">
+    <row r="732" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B732" s="7" t="s">
         <v>1829</v>
       </c>
-      <c r="C732" s="13" t="s">
+      <c r="C732" s="7" t="s">
         <v>1829</v>
       </c>
-      <c r="D732" s="13" t="s">
+      <c r="D732" s="7" t="s">
         <v>1830</v>
       </c>
       <c r="E732" s="7" t="s">
         <v>1828</v>
       </c>
-      <c r="F732" s="13" t="s">
+      <c r="F732" s="7" t="s">
         <v>1829</v>
       </c>
       <c r="G732" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="733">
-      <c r="B733" s="13" t="s">
+    <row r="733" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B733" s="7" t="s">
         <v>1831</v>
       </c>
-      <c r="C733" s="13" t="s">
+      <c r="C733" s="7" t="s">
         <v>1831</v>
       </c>
-      <c r="D733" s="13" t="s">
+      <c r="D733" s="7" t="s">
         <v>1832</v>
       </c>
       <c r="E733" s="7" t="s">
         <v>1828</v>
       </c>
-      <c r="F733" s="13" t="s">
+      <c r="F733" s="7" t="s">
         <v>1831</v>
       </c>
       <c r="G733" s="8" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="734" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C734" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D734" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E734" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F734" t="s">
+        <v>1833</v>
+      </c>
+      <c r="G734" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="735" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C735" s="14" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D735" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E735" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F735" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G735" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="736" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C736" s="15">
+        <v>4305910</v>
+      </c>
+      <c r="D736" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E736" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F736">
+        <v>4305910</v>
+      </c>
+      <c r="G736" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="737" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C737" s="15">
+        <v>4301840</v>
+      </c>
+      <c r="D737" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E737" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F737">
+        <v>4301840</v>
+      </c>
+      <c r="G737" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="738" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C738" s="15">
+        <v>4304514</v>
+      </c>
+      <c r="D738" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E738" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F738">
+        <v>4304514</v>
+      </c>
+      <c r="G738" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="739" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C739" s="15">
+        <v>4303673</v>
+      </c>
+      <c r="D739" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E739" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F739">
+        <v>4303673</v>
+      </c>
+      <c r="G739" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="740" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C740" s="15">
+        <v>5566508</v>
+      </c>
+      <c r="D740" t="s">
+        <v>1840</v>
+      </c>
+      <c r="E740" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F740">
+        <v>5566508</v>
+      </c>
+      <c r="G740" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="741" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C741" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D741" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E741" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F741" t="s">
+        <v>1842</v>
+      </c>
+      <c r="G741" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="742" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C742" s="15">
+        <v>4304510</v>
+      </c>
+      <c r="D742" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E742" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F742">
+        <v>4304510</v>
+      </c>
+      <c r="G742" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="743" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C743" s="13" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D743" t="s">
+        <v>1844</v>
+      </c>
+      <c r="E743" t="s">
+        <v>1802</v>
+      </c>
+      <c r="G743" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="744" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C744" s="15">
+        <v>16566</v>
+      </c>
+      <c r="D744" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E744" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F744">
+        <v>16566</v>
+      </c>
+      <c r="G744" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="745" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C745" s="15">
+        <v>14897</v>
+      </c>
+      <c r="D745" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E745" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F745">
+        <v>14897</v>
+      </c>
+      <c r="G745" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="746" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C746" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D746" t="s">
+        <v>425</v>
+      </c>
+      <c r="E746" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F746" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G746" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="747" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C747" s="15">
+        <v>4302393</v>
+      </c>
+      <c r="D747" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E747" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F747">
+        <v>4302393</v>
+      </c>
+      <c r="G747" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="748" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C748" s="15">
+        <v>5566510</v>
+      </c>
+      <c r="D748" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E748" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F748">
+        <v>5566510</v>
+      </c>
+      <c r="G748" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="749" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C749" s="15">
+        <v>4301795</v>
+      </c>
+      <c r="D749" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E749" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F749">
+        <v>4301795</v>
+      </c>
+      <c r="G749" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="750" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C750" s="15">
+        <v>16566</v>
+      </c>
+      <c r="D750" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E750" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F750" s="15">
+        <v>16566</v>
+      </c>
+      <c r="G750" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="751" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C751" s="15">
+        <v>14897</v>
+      </c>
+      <c r="D751" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E751" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F751" s="15">
+        <v>14897</v>
+      </c>
+      <c r="G751" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="752" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C752" s="15">
+        <v>4302393</v>
+      </c>
+      <c r="D752" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E752" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F752" s="15">
+        <v>4302393</v>
+      </c>
+      <c r="G752" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="753" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C753" s="15">
+        <v>4301795</v>
+      </c>
+      <c r="D753" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E753" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F753" s="15">
+        <v>4301795</v>
+      </c>
+      <c r="G753" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="754" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C754" s="15">
+        <v>4304510</v>
+      </c>
+      <c r="D754" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E754" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F754" s="15">
+        <v>4304510</v>
+      </c>
+      <c r="G754" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="755" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C755" s="15">
+        <v>4303673</v>
+      </c>
+      <c r="D755" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E755" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F755" s="15">
+        <v>4303673</v>
+      </c>
+      <c r="G755" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="756" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C756" s="15">
+        <v>4301840</v>
+      </c>
+      <c r="D756" t="s">
+        <v>1855</v>
+      </c>
+      <c r="E756" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F756" s="15">
+        <v>4301840</v>
+      </c>
+      <c r="G756" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="757" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C757" s="15">
+        <v>4304514</v>
+      </c>
+      <c r="D757" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E757" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F757" s="15">
+        <v>4304514</v>
+      </c>
+      <c r="G757" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="758" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C758" s="15">
+        <v>4305910</v>
+      </c>
+      <c r="D758" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E758" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F758" s="15">
+        <v>4305910</v>
+      </c>
+      <c r="G758" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="759" spans="3:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C759" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D759" t="s">
+        <v>1844</v>
+      </c>
+      <c r="E759" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F759" t="s">
+        <v>1845</v>
+      </c>
+      <c r="G759" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$G$733"/>
-  <drawing r:id="rId1"/>
+  <autoFilter ref="A1:G733" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>